--- a/极印版 aiken/AiKen JY Finance_261027.xlsx
+++ b/极印版 aiken/AiKen JY Finance_261027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a22fe4ae455d837/01 汉图/03 产品/06 Aiken/05. JY SI^MDO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="8_{8DB45FD7-6C93-40B1-8089-220C39B19EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2E5B6F9-B131-4EA9-910A-083F26C17BD4}"/>
+  <xr:revisionPtr revIDLastSave="314" documentId="8_{8DB45FD7-6C93-40B1-8089-220C39B19EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{607DDD7C-BCA8-4DAF-81F4-22CB77B9DEA8}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="787" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="787" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget" sheetId="15" r:id="rId1"/>
@@ -18,9 +18,10 @@
     <sheet name="分位表" sheetId="23" r:id="rId3"/>
     <sheet name="Scenarios" sheetId="6" r:id="rId4"/>
     <sheet name="BOM&amp;ASP" sheetId="4" r:id="rId5"/>
-    <sheet name="Normal Secnario" sheetId="2" r:id="rId6"/>
-    <sheet name="Best Secnario" sheetId="20" r:id="rId7"/>
-    <sheet name="Worst Secnario" sheetId="19" r:id="rId8"/>
+    <sheet name="财务读数" sheetId="24" r:id="rId6"/>
+    <sheet name="Normal Secnario" sheetId="2" r:id="rId7"/>
+    <sheet name="Best Secnario" sheetId="20" r:id="rId8"/>
+    <sheet name="Worst Secnario" sheetId="19" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="264">
   <si>
     <t>备注</t>
   </si>
@@ -208,9 +209,6 @@
   </si>
   <si>
     <t>Ricotta-P 海外</t>
-  </si>
-  <si>
-    <t>描述</t>
   </si>
   <si>
     <t>第一年</t>
@@ -468,22 +466,6 @@
     <phoneticPr fontId="33" type="noConversion"/>
   </si>
   <si>
-    <t>原127 人月，10月前约50，转极印后压缩20%</t>
-    <phoneticPr fontId="33" type="noConversion"/>
-  </si>
-  <si>
-    <t>线上渠道正常发挥（天猫/抖音/京东自营 + 达人分销）。</t>
-    <phoneticPr fontId="33" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品的仿胶卷卖点成为话题，得到市场接受，社媒有自来水传播。</t>
-    <phoneticPr fontId="33" type="noConversion"/>
-  </si>
-  <si>
-    <t>纯冷启动、社媒无传播、只靠自然流量和照片机存量转化。</t>
-    <phoneticPr fontId="33" type="noConversion"/>
-  </si>
-  <si>
     <t>AiKen 销量概率分布 · 读数表</t>
   </si>
   <si>
@@ -533,9 +515,6 @@
     <t>销量分位表 · 首年 &amp; 三年累计</t>
   </si>
   <si>
-    <t>读法：如「首年 P50 = 28,600」表示 50% 的模拟结果首年销量低于 28,600 台。淡黄行 = 会议三档场景锚。</t>
-  </si>
-  <si>
     <t>分位 P(x)</t>
   </si>
   <si>
@@ -681,9 +660,6 @@
   </si>
   <si>
     <t>三年累计</t>
-  </si>
-  <si>
-    <t>0.0%</t>
   </si>
   <si>
     <t>线上官旗比例</t>
@@ -698,27 +674,6 @@
     <phoneticPr fontId="33" type="noConversion"/>
   </si>
   <si>
-    <t>Worst 场景锚（月销 ≈ 1,459）</t>
-  </si>
-  <si>
-    <t>Normal 场景锚（月销 ≈ 2,196）</t>
-  </si>
-  <si>
-    <t>Best 场景锚（月销 ≈ 3,137）</t>
-  </si>
-  <si>
-    <t>P(≥ Worst 锚 17,513 台) — P10</t>
-    <phoneticPr fontId="33" type="noConversion"/>
-  </si>
-  <si>
-    <t>P(≥ Normal 锚 26,348 台) — P50</t>
-    <phoneticPr fontId="33" type="noConversion"/>
-  </si>
-  <si>
-    <t>P(≥ Best 锚 37,643 台) — P90</t>
-    <phoneticPr fontId="33" type="noConversion"/>
-  </si>
-  <si>
     <t>P(≥ 50,000 台)</t>
     <phoneticPr fontId="33" type="noConversion"/>
   </si>
@@ -731,27 +686,184 @@
     <phoneticPr fontId="33" type="noConversion"/>
   </si>
   <si>
-    <t>注：本表由 v0.3 模拟结果（v03_results.npz）直接计算生成；漏斗参数为 S1 实测校准（2026-10-26）。</t>
-    <phoneticPr fontId="33" type="noConversion"/>
-  </si>
-  <si>
     <t>10月前人月</t>
     <phoneticPr fontId="33" type="noConversion"/>
   </si>
   <si>
-    <t>NRE</t>
-    <phoneticPr fontId="33" type="noConversion"/>
-  </si>
-  <si>
-    <t>总和</t>
-    <phoneticPr fontId="33" type="noConversion"/>
-  </si>
-  <si>
     <t>ASP</t>
     <phoneticPr fontId="33" type="noConversion"/>
   </si>
   <si>
     <t>BOM</t>
+    <phoneticPr fontId="33" type="noConversion"/>
+  </si>
+  <si>
+    <t>P50</t>
+    <phoneticPr fontId="33" type="noConversion"/>
+  </si>
+  <si>
+    <t>P10</t>
+    <phoneticPr fontId="33" type="noConversion"/>
+  </si>
+  <si>
+    <t>P90</t>
+    <phoneticPr fontId="33" type="noConversion"/>
+  </si>
+  <si>
+    <t>分布</t>
+    <phoneticPr fontId="33" type="noConversion"/>
+  </si>
+  <si>
+    <t>原127 人月，10月前约36</t>
+    <phoneticPr fontId="33" type="noConversion"/>
+  </si>
+  <si>
+    <t>Worst 场景锚（月销 ≈ 1,192）</t>
+  </si>
+  <si>
+    <t>Normal 场景锚（月销 ≈ 1,834）</t>
+  </si>
+  <si>
+    <t>Best 场景锚（月销 ≈ 2,678）</t>
+  </si>
+  <si>
+    <t>P(≥ Worst 锚 14,300 台) — P10</t>
+    <phoneticPr fontId="33" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(≥ Normal 锚 22,009 台) — P50</t>
+    <phoneticPr fontId="33" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(≥ Best 锚 32,139 台) — P90</t>
+    <phoneticPr fontId="33" type="noConversion"/>
+  </si>
+  <si>
+    <t>已发生NRE</t>
+    <phoneticPr fontId="33" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉没成本总和</t>
+    <phoneticPr fontId="33" type="noConversion"/>
+  </si>
+  <si>
+    <t>单台净贡献 51.9 元（ASP不含税431.2×70%−BOM250）· 分布 = v0.4 · 与读数表/评审页同源</t>
+  </si>
+  <si>
+    <t>指标</t>
+  </si>
+  <si>
+    <t>Worst (P10)</t>
+  </si>
+  <si>
+    <t>Normal (P50)</t>
+  </si>
+  <si>
+    <t>Best (P90)</t>
+  </si>
+  <si>
+    <t>14,300</t>
+  </si>
+  <si>
+    <t>22,009</t>
+  </si>
+  <si>
+    <t>32,139</t>
+  </si>
+  <si>
+    <t>首年净贡献（万元）</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>首年投入覆盖</t>
+  </si>
+  <si>
+    <t>16%</t>
+  </si>
+  <si>
+    <t>24%</t>
+  </si>
+  <si>
+    <t>35%</t>
+  </si>
+  <si>
+    <t>32,985</t>
+  </si>
+  <si>
+    <t>63,130</t>
+  </si>
+  <si>
+    <t>103,850</t>
+  </si>
+  <si>
+    <t>三年累计净利（万元）</t>
+  </si>
+  <si>
+    <t>-306</t>
+  </si>
+  <si>
+    <t>-150</t>
+  </si>
+  <si>
+    <t>+62</t>
+  </si>
+  <si>
+    <t>全分布读数</t>
+  </si>
+  <si>
+    <t>P(首年投入覆盖 ≥100%)</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>P(三年累计转正)</t>
+  </si>
+  <si>
+    <t>17.0%</t>
+  </si>
+  <si>
+    <t>P(三年净利 ≥ +100万)</t>
+  </si>
+  <si>
+    <t>7.1%</t>
+  </si>
+  <si>
+    <t>P(三年净亏 &gt; 200万)</t>
+  </si>
+  <si>
+    <t>34.7%</t>
+  </si>
+  <si>
+    <t>P(三年累计 ≥10万台)</t>
+  </si>
+  <si>
+    <t>12%</t>
+  </si>
+  <si>
+    <t>注：本表为「简化口径」（单台净贡献×销量−投资），不含模具摊销分年/资金成本/MOH等细节；</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    精确口径以财务表 Excel Scenario sheets 为准（Normal −140万/Best +1.6万/Worst −234万）。</t>
+  </si>
+  <si>
+    <t>AiKen 财务读数</t>
+    <phoneticPr fontId="43" type="noConversion"/>
+  </si>
+  <si>
+    <t>注：本表由 v0.4 模拟结果（v04_results.npz）直接计算生成；漏斗参数为 S1 实测校准（2026-10-26）。</t>
+    <phoneticPr fontId="33" type="noConversion"/>
+  </si>
+  <si>
+    <t>读法：如「首年 P50 = 22,009」表示 50% 的模拟结果首年销量低于 28,600 台。淡黄行 = 会议三档场景锚。</t>
     <phoneticPr fontId="33" type="noConversion"/>
   </si>
 </sst>
@@ -771,7 +883,7 @@
     <numFmt numFmtId="183" formatCode="\¥#,##0_);[Red]\(\¥#,##0\)"/>
     <numFmt numFmtId="184" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="46">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1084,6 +1196,33 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -1198,7 +1337,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="58">
+  <borders count="59">
     <border>
       <left/>
       <right/>
@@ -1907,6 +2046,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1943,7 +2097,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2090,9 +2244,6 @@
     </xf>
     <xf numFmtId="176" fontId="10" fillId="8" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="3" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2406,73 +2557,86 @@
     <xf numFmtId="176" fontId="15" fillId="3" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="181" fontId="9" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="37" fillId="17" borderId="53" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="45" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="22" fillId="13" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="18" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="18" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="22" fillId="13" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="18" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="18" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="17" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="17" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2812,1385 +2976,1384 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A2" s="106"/>
-      <c r="B2" s="107" t="s">
+      <c r="A2" s="105"/>
+      <c r="B2" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="108" t="s">
+      <c r="C2" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="108" t="s">
+      <c r="D2" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="108" t="s">
+      <c r="E2" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="109"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="112" t="s">
+      <c r="F2" s="108"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="111" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A3" s="106"/>
-      <c r="B3" s="113" t="s">
+      <c r="A3" s="105"/>
+      <c r="B3" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="114" t="s">
+      <c r="C3" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="115" t="e">
+      <c r="D3" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E3" s="116" t="s">
+      <c r="E3" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="117"/>
-      <c r="G3" s="118" t="s">
+      <c r="F3" s="116"/>
+      <c r="G3" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="119">
+      <c r="H3" s="118">
         <v>600000</v>
       </c>
-      <c r="I3" s="120"/>
+      <c r="I3" s="119"/>
     </row>
     <row r="4" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A4" s="106"/>
-      <c r="B4" s="113" t="s">
+      <c r="A4" s="105"/>
+      <c r="B4" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="115" t="e">
+      <c r="D4" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E4" s="116" t="s">
+      <c r="E4" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="117"/>
-      <c r="G4" s="118" t="s">
+      <c r="F4" s="116"/>
+      <c r="G4" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="119">
-        <v>715000</v>
-      </c>
-      <c r="I4" s="120"/>
+      <c r="H4" s="118">
+        <v>500000</v>
+      </c>
+      <c r="I4" s="119"/>
     </row>
     <row r="5" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A5" s="106"/>
-      <c r="B5" s="113" t="s">
+      <c r="A5" s="105"/>
+      <c r="B5" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="115" t="e">
+      <c r="D5" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E5" s="116" t="s">
+      <c r="E5" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="117"/>
-      <c r="G5" s="118" t="s">
+      <c r="F5" s="116"/>
+      <c r="G5" s="117" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="119">
-        <f>781250-H13</f>
-        <v>481250</v>
-      </c>
-      <c r="I5" s="120"/>
+      <c r="H5" s="118">
+        <v>375550</v>
+      </c>
+      <c r="I5" s="119"/>
     </row>
     <row r="6" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A6" s="106"/>
-      <c r="B6" s="113" t="s">
+      <c r="A6" s="105"/>
+      <c r="B6" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="114" t="s">
+      <c r="C6" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="115" t="e">
+      <c r="D6" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E6" s="116" t="s">
+      <c r="E6" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="117"/>
-      <c r="G6" s="118" t="s">
+      <c r="F6" s="116"/>
+      <c r="G6" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="119">
-        <v>159000</v>
-      </c>
-      <c r="I6" s="120"/>
+      <c r="H6" s="118">
+        <v>145000</v>
+      </c>
+      <c r="I6" s="119"/>
     </row>
     <row r="7" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A7" s="106"/>
-      <c r="B7" s="113" t="s">
+      <c r="A7" s="105"/>
+      <c r="B7" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="114" t="s">
+      <c r="C7" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="115" t="e">
+      <c r="D7" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E7" s="116" t="s">
+      <c r="E7" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="117"/>
-      <c r="G7" s="118" t="s">
+      <c r="F7" s="116"/>
+      <c r="G7" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="119">
+      <c r="H7" s="118">
         <v>150000</v>
       </c>
-      <c r="I7" s="120"/>
+      <c r="I7" s="119"/>
     </row>
     <row r="8" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A8" s="106"/>
-      <c r="B8" s="113" t="s">
+      <c r="A8" s="105"/>
+      <c r="B8" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="114" t="s">
+      <c r="C8" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="115" t="e">
+      <c r="D8" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E8" s="116" t="s">
+      <c r="E8" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="117"/>
-      <c r="G8" s="118" t="s">
+      <c r="F8" s="116"/>
+      <c r="G8" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="119">
-        <f>(127-50)*33000*0.8</f>
-        <v>2032800</v>
-      </c>
-      <c r="I8" s="136" t="s">
-        <v>139</v>
+      <c r="H8" s="118">
+        <f>(127-36)*33000</f>
+        <v>3003000</v>
+      </c>
+      <c r="I8" s="135" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A9" s="106"/>
-      <c r="B9" s="113" t="s">
+      <c r="A9" s="105"/>
+      <c r="B9" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="114" t="s">
+      <c r="C9" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="115" t="e">
+      <c r="D9" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E9" s="116" t="s">
+      <c r="E9" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="117"/>
-      <c r="G9" s="121" t="s">
+      <c r="F9" s="116"/>
+      <c r="G9" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="122">
+      <c r="H9" s="121">
         <f>SUM(H3:H8)</f>
-        <v>4138050</v>
-      </c>
-      <c r="I9" s="123"/>
+        <v>4773550</v>
+      </c>
+      <c r="I9" s="122"/>
     </row>
     <row r="10" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A10" s="106"/>
-      <c r="B10" s="113" t="s">
+      <c r="A10" s="105"/>
+      <c r="B10" s="112" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="115" t="e">
+      <c r="D10" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E10" s="115" t="s">
+      <c r="E10" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="117"/>
+      <c r="F10" s="116"/>
     </row>
     <row r="11" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A11" s="106"/>
-      <c r="B11" s="113" t="s">
+      <c r="A11" s="105"/>
+      <c r="B11" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="114" t="s">
+      <c r="C11" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="115" t="e">
+      <c r="D11" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E11" s="115" t="s">
+      <c r="E11" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="117"/>
+      <c r="F11" s="116"/>
     </row>
     <row r="12" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A12" s="106"/>
-      <c r="B12" s="113" t="s">
+      <c r="A12" s="105"/>
+      <c r="B12" s="112" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="114" t="s">
+      <c r="C12" s="113" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="115" t="e">
+      <c r="D12" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E12" s="115" t="s">
+      <c r="E12" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="117"/>
-      <c r="G12" s="164" t="s">
-        <v>138</v>
-      </c>
-      <c r="H12" s="119">
-        <f>50*33000</f>
-        <v>1650000</v>
-      </c>
-      <c r="I12" s="154" t="s">
-        <v>223</v>
+      <c r="F12" s="116"/>
+      <c r="G12" s="168" t="s">
+        <v>137</v>
+      </c>
+      <c r="H12" s="118">
+        <f>36*33000</f>
+        <v>1188000</v>
+      </c>
+      <c r="I12" s="153" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A13" s="168"/>
-      <c r="B13" s="113" t="s">
+      <c r="A13" s="172"/>
+      <c r="B13" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="114" t="s">
+      <c r="C13" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="115" t="e">
+      <c r="D13" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E13" s="115" t="s">
+      <c r="E13" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="117"/>
-      <c r="G13" s="165"/>
-      <c r="H13" s="119">
-        <v>300000</v>
-      </c>
-      <c r="I13" s="154" t="s">
-        <v>224</v>
+      <c r="F13" s="116"/>
+      <c r="G13" s="169"/>
+      <c r="H13" s="118">
+        <v>634700</v>
+      </c>
+      <c r="I13" s="153" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A14" s="169"/>
-      <c r="B14" s="113" t="s">
+      <c r="A14" s="173"/>
+      <c r="B14" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="114" t="s">
+      <c r="C14" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="115" t="e">
+      <c r="D14" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E14" s="115" t="s">
+      <c r="E14" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="117"/>
-      <c r="G14" s="165"/>
-      <c r="H14" s="119">
+      <c r="F14" s="116"/>
+      <c r="G14" s="169"/>
+      <c r="H14" s="118">
         <f>H12+H13</f>
-        <v>1950000</v>
-      </c>
-      <c r="I14" s="155" t="s">
-        <v>225</v>
+        <v>1822700</v>
+      </c>
+      <c r="I14" s="154" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A15" s="169"/>
-      <c r="B15" s="113" t="s">
+      <c r="A15" s="173"/>
+      <c r="B15" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="115" t="e">
+      <c r="D15" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E15" s="115" t="s">
+      <c r="E15" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="117"/>
+      <c r="F15" s="116"/>
     </row>
     <row r="16" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A16" s="106"/>
-      <c r="B16" s="113" t="s">
+      <c r="A16" s="105"/>
+      <c r="B16" s="112" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="114" t="s">
+      <c r="C16" s="113" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="115" t="e">
+      <c r="D16" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E16" s="115" t="s">
+      <c r="E16" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="117"/>
+      <c r="F16" s="116"/>
     </row>
     <row r="17" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A17" s="106"/>
-      <c r="B17" s="113" t="s">
+      <c r="A17" s="105"/>
+      <c r="B17" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="114" t="s">
+      <c r="C17" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="115" t="e">
+      <c r="D17" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E17" s="115" t="s">
+      <c r="E17" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="117"/>
+      <c r="F17" s="116"/>
     </row>
     <row r="18" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A18" s="106"/>
-      <c r="B18" s="113" t="s">
+      <c r="A18" s="105"/>
+      <c r="B18" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="114" t="s">
+      <c r="C18" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="115" t="e">
+      <c r="D18" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E18" s="115" t="s">
+      <c r="E18" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="117"/>
+      <c r="F18" s="116"/>
     </row>
     <row r="19" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A19" s="106"/>
-      <c r="B19" s="113" t="s">
+      <c r="A19" s="105"/>
+      <c r="B19" s="112" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="114" t="s">
+      <c r="C19" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="115" t="e">
+      <c r="D19" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E19" s="115" t="s">
+      <c r="E19" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="117"/>
+      <c r="F19" s="116"/>
     </row>
     <row r="20" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A20" s="106"/>
-      <c r="B20" s="113" t="s">
+      <c r="A20" s="105"/>
+      <c r="B20" s="112" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="114" t="s">
+      <c r="C20" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="115" t="e">
+      <c r="D20" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E20" s="115" t="s">
+      <c r="E20" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="117"/>
+      <c r="F20" s="116"/>
     </row>
     <row r="21" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A21" s="106"/>
-      <c r="B21" s="113" t="s">
+      <c r="A21" s="105"/>
+      <c r="B21" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="114" t="s">
+      <c r="C21" s="113" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="115" t="e">
+      <c r="D21" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E21" s="115" t="s">
+      <c r="E21" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F21" s="117"/>
+      <c r="F21" s="116"/>
     </row>
     <row r="22" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A22" s="106"/>
-      <c r="B22" s="113" t="s">
+      <c r="A22" s="105"/>
+      <c r="B22" s="112" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="114" t="s">
+      <c r="C22" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="115" t="e">
+      <c r="D22" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E22" s="115" t="s">
+      <c r="E22" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="117"/>
+      <c r="F22" s="116"/>
     </row>
     <row r="23" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A23" s="106"/>
-      <c r="B23" s="117"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="117"/>
+      <c r="A23" s="105"/>
+      <c r="B23" s="116"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="114"/>
+      <c r="E23" s="114"/>
+      <c r="F23" s="116"/>
     </row>
     <row r="24" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A24" s="106"/>
-      <c r="B24" s="117"/>
-      <c r="C24" s="125" t="s">
+      <c r="A24" s="105"/>
+      <c r="B24" s="116"/>
+      <c r="C24" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="126"/>
-      <c r="E24" s="126"/>
-      <c r="F24" s="127"/>
+      <c r="D24" s="125"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="126"/>
     </row>
     <row r="25" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A25" s="106"/>
-      <c r="B25" s="117"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="117"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="117"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="106"/>
+      <c r="A25" s="105"/>
+      <c r="B25" s="116"/>
+      <c r="C25" s="116"/>
+      <c r="D25" s="116"/>
+      <c r="E25" s="116"/>
+      <c r="F25" s="116"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
     </row>
     <row r="26" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A26" s="106"/>
-      <c r="B26" s="117"/>
-      <c r="C26" s="128" t="s">
+      <c r="A26" s="105"/>
+      <c r="B26" s="116"/>
+      <c r="C26" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="166" t="e">
+      <c r="D26" s="170" t="e">
         <f>SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="E26" s="167"/>
-      <c r="F26" s="129"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="106"/>
+      <c r="E26" s="171"/>
+      <c r="F26" s="128"/>
+      <c r="G26" s="105"/>
+      <c r="H26" s="105"/>
     </row>
     <row r="27" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A27" s="106"/>
-      <c r="B27" s="117"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="117"/>
-      <c r="E27" s="117"/>
-      <c r="F27" s="117"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="106"/>
+      <c r="A27" s="105"/>
+      <c r="B27" s="116"/>
+      <c r="C27" s="116"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="116"/>
+      <c r="F27" s="116"/>
+      <c r="G27" s="105"/>
+      <c r="H27" s="105"/>
     </row>
     <row r="28" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A28" s="106"/>
-      <c r="B28" s="106"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="106"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="106"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="106"/>
+      <c r="A28" s="105"/>
+      <c r="B28" s="105"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="105"/>
+      <c r="H28" s="105"/>
     </row>
     <row r="29" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A29" s="106"/>
-      <c r="B29" s="106"/>
-      <c r="C29" s="106"/>
-      <c r="D29" s="106"/>
-      <c r="E29" s="106"/>
-      <c r="F29" s="106"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="106"/>
+      <c r="A29" s="105"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="105"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="105"/>
+      <c r="H29" s="105"/>
     </row>
     <row r="31" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A31" s="106"/>
-      <c r="B31" s="130" t="s">
+      <c r="A31" s="105"/>
+      <c r="B31" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="131">
+      <c r="C31" s="130">
         <v>45587</v>
       </c>
-      <c r="D31" s="132"/>
-      <c r="E31" s="132"/>
-      <c r="F31" s="132"/>
-      <c r="G31" s="106"/>
-      <c r="H31" s="106"/>
-    </row>
-    <row r="32" spans="1:8" s="105" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A32" s="133"/>
-      <c r="B32" s="133"/>
-      <c r="C32" s="133"/>
-      <c r="D32" s="133"/>
-      <c r="E32" s="133"/>
-      <c r="F32" s="133"/>
+      <c r="D31" s="131"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="131"/>
+      <c r="G31" s="105"/>
+      <c r="H31" s="105"/>
+    </row>
+    <row r="32" spans="1:8" s="104" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A32" s="132"/>
+      <c r="B32" s="132"/>
+      <c r="C32" s="132"/>
+      <c r="D32" s="132"/>
+      <c r="E32" s="132"/>
+      <c r="F32" s="132"/>
     </row>
     <row r="33" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A33" s="106"/>
-      <c r="B33" s="134"/>
-      <c r="C33" s="115"/>
-      <c r="D33" s="116"/>
-      <c r="E33" s="116"/>
-      <c r="F33" s="117"/>
+      <c r="A33" s="105"/>
+      <c r="B33" s="133"/>
+      <c r="C33" s="114"/>
+      <c r="D33" s="115"/>
+      <c r="E33" s="115"/>
+      <c r="F33" s="116"/>
     </row>
     <row r="34" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A34" s="106"/>
-      <c r="B34" s="107" t="s">
+      <c r="A34" s="105"/>
+      <c r="B34" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="108" t="s">
+      <c r="C34" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="108" t="s">
+      <c r="D34" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="E34" s="108" t="s">
+      <c r="E34" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="F34" s="109"/>
+      <c r="F34" s="108"/>
     </row>
     <row r="35" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A35" s="106"/>
-      <c r="B35" s="113" t="s">
+      <c r="A35" s="105"/>
+      <c r="B35" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="114" t="s">
+      <c r="C35" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="D35" s="115" t="e">
+      <c r="D35" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E35" s="115" t="s">
+      <c r="E35" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F35" s="117"/>
+      <c r="F35" s="116"/>
     </row>
     <row r="36" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A36" s="106"/>
-      <c r="B36" s="113" t="s">
+      <c r="A36" s="105"/>
+      <c r="B36" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="114" t="s">
+      <c r="C36" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="115" t="e">
+      <c r="D36" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E36" s="115" t="s">
+      <c r="E36" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F36" s="117"/>
+      <c r="F36" s="116"/>
     </row>
     <row r="37" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A37" s="106"/>
-      <c r="B37" s="113" t="s">
+      <c r="A37" s="105"/>
+      <c r="B37" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="114" t="s">
+      <c r="C37" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="115" t="e">
+      <c r="D37" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E37" s="115" t="s">
+      <c r="E37" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F37" s="117"/>
+      <c r="F37" s="116"/>
     </row>
     <row r="38" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A38" s="106"/>
-      <c r="B38" s="113" t="s">
+      <c r="A38" s="105"/>
+      <c r="B38" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="114" t="s">
+      <c r="C38" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="D38" s="115" t="e">
+      <c r="D38" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E38" s="115" t="s">
+      <c r="E38" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F38" s="117"/>
+      <c r="F38" s="116"/>
     </row>
     <row r="39" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A39" s="106"/>
-      <c r="B39" s="113" t="s">
+      <c r="A39" s="105"/>
+      <c r="B39" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="114" t="s">
+      <c r="C39" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="D39" s="115" t="e">
+      <c r="D39" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E39" s="115" t="s">
+      <c r="E39" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F39" s="117"/>
+      <c r="F39" s="116"/>
     </row>
     <row r="40" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A40" s="106"/>
-      <c r="B40" s="113" t="s">
+      <c r="A40" s="105"/>
+      <c r="B40" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="114" t="s">
+      <c r="C40" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="115" t="e">
+      <c r="D40" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E40" s="115" t="s">
+      <c r="E40" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F40" s="117"/>
+      <c r="F40" s="116"/>
     </row>
     <row r="41" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A41" s="106"/>
-      <c r="B41" s="113" t="s">
+      <c r="A41" s="105"/>
+      <c r="B41" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="114" t="s">
+      <c r="C41" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="D41" s="115" t="e">
+      <c r="D41" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E41" s="115" t="s">
+      <c r="E41" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F41" s="117"/>
+      <c r="F41" s="116"/>
     </row>
     <row r="42" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A42" s="106"/>
-      <c r="B42" s="113" t="s">
+      <c r="A42" s="105"/>
+      <c r="B42" s="112" t="s">
         <v>27</v>
       </c>
-      <c r="C42" s="114" t="s">
+      <c r="C42" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="D42" s="115" t="e">
+      <c r="D42" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E42" s="115" t="s">
+      <c r="E42" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F42" s="117"/>
+      <c r="F42" s="116"/>
     </row>
     <row r="43" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A43" s="106"/>
-      <c r="B43" s="113" t="s">
+      <c r="A43" s="105"/>
+      <c r="B43" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="C43" s="114" t="s">
+      <c r="C43" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="D43" s="115" t="e">
+      <c r="D43" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E43" s="115" t="s">
+      <c r="E43" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F43" s="117"/>
+      <c r="F43" s="116"/>
     </row>
     <row r="44" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A44" s="106"/>
-      <c r="B44" s="113" t="s">
+      <c r="A44" s="105"/>
+      <c r="B44" s="112" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="114" t="s">
+      <c r="C44" s="113" t="s">
         <v>32</v>
       </c>
-      <c r="D44" s="115" t="e">
+      <c r="D44" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E44" s="115" t="s">
+      <c r="E44" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F44" s="117"/>
+      <c r="F44" s="116"/>
     </row>
     <row r="45" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A45" s="168"/>
-      <c r="B45" s="113" t="s">
+      <c r="A45" s="172"/>
+      <c r="B45" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="C45" s="114" t="s">
+      <c r="C45" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="D45" s="115" t="e">
+      <c r="D45" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E45" s="115" t="s">
+      <c r="E45" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F45" s="117"/>
+      <c r="F45" s="116"/>
     </row>
     <row r="46" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A46" s="169"/>
-      <c r="B46" s="113" t="s">
+      <c r="A46" s="173"/>
+      <c r="B46" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="C46" s="114" t="s">
+      <c r="C46" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="D46" s="115" t="e">
+      <c r="D46" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E46" s="115" t="s">
+      <c r="E46" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F46" s="117"/>
+      <c r="F46" s="116"/>
     </row>
     <row r="47" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A47" s="169"/>
-      <c r="B47" s="113" t="s">
+      <c r="A47" s="173"/>
+      <c r="B47" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="114" t="s">
+      <c r="C47" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="D47" s="115" t="e">
+      <c r="D47" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E47" s="115" t="s">
+      <c r="E47" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F47" s="117"/>
+      <c r="F47" s="116"/>
     </row>
     <row r="48" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A48" s="106"/>
-      <c r="B48" s="113" t="s">
+      <c r="A48" s="105"/>
+      <c r="B48" s="112" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="114" t="s">
+      <c r="C48" s="113" t="s">
         <v>39</v>
       </c>
-      <c r="D48" s="115" t="e">
+      <c r="D48" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E48" s="115" t="s">
+      <c r="E48" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F48" s="117"/>
+      <c r="F48" s="116"/>
     </row>
     <row r="49" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A49" s="106"/>
-      <c r="B49" s="113" t="s">
+      <c r="A49" s="105"/>
+      <c r="B49" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="C49" s="114" t="s">
+      <c r="C49" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D49" s="115" t="e">
+      <c r="D49" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E49" s="115" t="s">
+      <c r="E49" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F49" s="117"/>
+      <c r="F49" s="116"/>
     </row>
     <row r="50" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A50" s="106"/>
-      <c r="B50" s="113" t="s">
+      <c r="A50" s="105"/>
+      <c r="B50" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="C50" s="114" t="s">
+      <c r="C50" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="D50" s="115" t="e">
+      <c r="D50" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E50" s="115" t="s">
+      <c r="E50" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F50" s="117"/>
+      <c r="F50" s="116"/>
     </row>
     <row r="51" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A51" s="106"/>
-      <c r="B51" s="113" t="s">
+      <c r="A51" s="105"/>
+      <c r="B51" s="112" t="s">
         <v>44</v>
       </c>
-      <c r="C51" s="114" t="s">
+      <c r="C51" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="D51" s="115" t="e">
+      <c r="D51" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E51" s="115" t="s">
+      <c r="E51" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F51" s="117"/>
+      <c r="F51" s="116"/>
     </row>
     <row r="52" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A52" s="106"/>
-      <c r="B52" s="113" t="s">
+      <c r="A52" s="105"/>
+      <c r="B52" s="112" t="s">
         <v>46</v>
       </c>
-      <c r="C52" s="114" t="s">
+      <c r="C52" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="D52" s="115" t="e">
+      <c r="D52" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E52" s="115" t="s">
+      <c r="E52" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F52" s="117"/>
+      <c r="F52" s="116"/>
     </row>
     <row r="53" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A53" s="106"/>
-      <c r="B53" s="113" t="s">
+      <c r="A53" s="105"/>
+      <c r="B53" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="114" t="s">
+      <c r="C53" s="113" t="s">
         <v>49</v>
       </c>
-      <c r="D53" s="115" t="e">
+      <c r="D53" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E53" s="115" t="s">
+      <c r="E53" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F53" s="117"/>
+      <c r="F53" s="116"/>
     </row>
     <row r="54" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A54" s="106"/>
-      <c r="B54" s="113" t="s">
+      <c r="A54" s="105"/>
+      <c r="B54" s="112" t="s">
         <v>50</v>
       </c>
-      <c r="C54" s="114" t="s">
+      <c r="C54" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="D54" s="115" t="e">
+      <c r="D54" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E54" s="115" t="s">
+      <c r="E54" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F54" s="117"/>
+      <c r="F54" s="116"/>
     </row>
     <row r="55" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A55" s="106"/>
-      <c r="B55" s="117"/>
-      <c r="C55" s="124"/>
-      <c r="D55" s="115"/>
-      <c r="E55" s="115"/>
-      <c r="F55" s="117"/>
+      <c r="A55" s="105"/>
+      <c r="B55" s="116"/>
+      <c r="C55" s="123"/>
+      <c r="D55" s="114"/>
+      <c r="E55" s="114"/>
+      <c r="F55" s="116"/>
     </row>
     <row r="56" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A56" s="106"/>
-      <c r="B56" s="117"/>
-      <c r="C56" s="125" t="s">
+      <c r="A56" s="105"/>
+      <c r="B56" s="116"/>
+      <c r="C56" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="D56" s="126"/>
-      <c r="E56" s="126"/>
-      <c r="F56" s="127"/>
+      <c r="D56" s="125"/>
+      <c r="E56" s="125"/>
+      <c r="F56" s="126"/>
     </row>
     <row r="57" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A57" s="106"/>
-      <c r="B57" s="117"/>
-      <c r="C57" s="117"/>
-      <c r="D57" s="117"/>
-      <c r="E57" s="117"/>
-      <c r="F57" s="117"/>
-      <c r="G57" s="106"/>
-      <c r="H57" s="106"/>
+      <c r="A57" s="105"/>
+      <c r="B57" s="116"/>
+      <c r="C57" s="116"/>
+      <c r="D57" s="116"/>
+      <c r="E57" s="116"/>
+      <c r="F57" s="116"/>
+      <c r="G57" s="105"/>
+      <c r="H57" s="105"/>
     </row>
     <row r="58" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A58" s="106"/>
-      <c r="B58" s="117"/>
-      <c r="C58" s="128" t="s">
+      <c r="A58" s="105"/>
+      <c r="B58" s="116"/>
+      <c r="C58" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="D58" s="166" t="e">
+      <c r="D58" s="170" t="e">
         <f>SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="E58" s="167"/>
-      <c r="F58" s="129"/>
-      <c r="G58" s="106"/>
-      <c r="H58" s="106"/>
+      <c r="E58" s="171"/>
+      <c r="F58" s="128"/>
+      <c r="G58" s="105"/>
+      <c r="H58" s="105"/>
     </row>
     <row r="63" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A63" s="106"/>
-      <c r="B63" s="106"/>
-      <c r="C63" s="106"/>
-      <c r="D63" s="106"/>
-      <c r="E63" s="106"/>
-      <c r="F63" s="106"/>
-      <c r="G63" s="106"/>
-      <c r="H63" s="106"/>
+      <c r="A63" s="105"/>
+      <c r="B63" s="105"/>
+      <c r="C63" s="105"/>
+      <c r="D63" s="105"/>
+      <c r="E63" s="105"/>
+      <c r="F63" s="105"/>
+      <c r="G63" s="105"/>
+      <c r="H63" s="105"/>
     </row>
     <row r="65" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A65" s="106"/>
-      <c r="B65" s="130" t="s">
+      <c r="A65" s="105"/>
+      <c r="B65" s="129" t="s">
         <v>55</v>
       </c>
-      <c r="C65" s="131">
+      <c r="C65" s="130">
         <v>45587</v>
       </c>
-      <c r="D65" s="132"/>
-      <c r="E65" s="132"/>
-      <c r="F65" s="132"/>
-      <c r="G65" s="106"/>
-      <c r="H65" s="106"/>
-    </row>
-    <row r="66" spans="1:8" s="105" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A66" s="133"/>
-      <c r="B66" s="133"/>
-      <c r="C66" s="133"/>
-      <c r="D66" s="133"/>
-      <c r="E66" s="133"/>
-      <c r="F66" s="133"/>
+      <c r="D65" s="131"/>
+      <c r="E65" s="131"/>
+      <c r="F65" s="131"/>
+      <c r="G65" s="105"/>
+      <c r="H65" s="105"/>
+    </row>
+    <row r="66" spans="1:8" s="104" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A66" s="132"/>
+      <c r="B66" s="132"/>
+      <c r="C66" s="132"/>
+      <c r="D66" s="132"/>
+      <c r="E66" s="132"/>
+      <c r="F66" s="132"/>
     </row>
     <row r="67" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A67" s="106"/>
-      <c r="B67" s="134"/>
-      <c r="C67" s="115"/>
-      <c r="D67" s="116"/>
-      <c r="E67" s="116"/>
-      <c r="F67" s="117"/>
+      <c r="A67" s="105"/>
+      <c r="B67" s="133"/>
+      <c r="C67" s="114"/>
+      <c r="D67" s="115"/>
+      <c r="E67" s="115"/>
+      <c r="F67" s="116"/>
     </row>
     <row r="68" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A68" s="106"/>
-      <c r="B68" s="107" t="s">
+      <c r="A68" s="105"/>
+      <c r="B68" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="C68" s="108" t="s">
+      <c r="C68" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="D68" s="108" t="s">
+      <c r="D68" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="E68" s="108" t="s">
+      <c r="E68" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="F68" s="109"/>
+      <c r="F68" s="108"/>
     </row>
     <row r="69" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A69" s="106"/>
-      <c r="B69" s="113" t="s">
+      <c r="A69" s="105"/>
+      <c r="B69" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="C69" s="114" t="s">
+      <c r="C69" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="D69" s="115" t="e">
+      <c r="D69" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E69" s="115" t="s">
+      <c r="E69" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F69" s="117"/>
+      <c r="F69" s="116"/>
     </row>
     <row r="70" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A70" s="106"/>
-      <c r="B70" s="113" t="s">
+      <c r="A70" s="105"/>
+      <c r="B70" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="C70" s="114" t="s">
+      <c r="C70" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="D70" s="115" t="e">
+      <c r="D70" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E70" s="115" t="s">
+      <c r="E70" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F70" s="117"/>
+      <c r="F70" s="116"/>
     </row>
     <row r="71" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A71" s="106"/>
-      <c r="B71" s="113" t="s">
+      <c r="A71" s="105"/>
+      <c r="B71" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="C71" s="114" t="s">
+      <c r="C71" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="D71" s="115" t="e">
+      <c r="D71" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E71" s="115" t="s">
+      <c r="E71" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F71" s="117"/>
+      <c r="F71" s="116"/>
     </row>
     <row r="72" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A72" s="106"/>
-      <c r="B72" s="113" t="s">
+      <c r="A72" s="105"/>
+      <c r="B72" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="C72" s="114" t="s">
+      <c r="C72" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="D72" s="115" t="e">
+      <c r="D72" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E72" s="115" t="s">
+      <c r="E72" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F72" s="117"/>
+      <c r="F72" s="116"/>
     </row>
     <row r="73" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A73" s="106"/>
-      <c r="B73" s="113" t="s">
+      <c r="A73" s="105"/>
+      <c r="B73" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="C73" s="114" t="s">
+      <c r="C73" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="D73" s="115" t="e">
+      <c r="D73" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E73" s="115" t="s">
+      <c r="E73" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F73" s="117"/>
+      <c r="F73" s="116"/>
     </row>
     <row r="74" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A74" s="106"/>
-      <c r="B74" s="113" t="s">
+      <c r="A74" s="105"/>
+      <c r="B74" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="114" t="s">
+      <c r="C74" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="D74" s="115" t="e">
+      <c r="D74" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E74" s="115" t="s">
+      <c r="E74" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F74" s="117"/>
+      <c r="F74" s="116"/>
     </row>
     <row r="75" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A75" s="106"/>
-      <c r="B75" s="113" t="s">
+      <c r="A75" s="105"/>
+      <c r="B75" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="C75" s="114" t="s">
+      <c r="C75" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="D75" s="115" t="e">
+      <c r="D75" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E75" s="115" t="s">
+      <c r="E75" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F75" s="117"/>
+      <c r="F75" s="116"/>
     </row>
     <row r="76" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A76" s="106"/>
-      <c r="B76" s="113" t="s">
+      <c r="A76" s="105"/>
+      <c r="B76" s="112" t="s">
         <v>27</v>
       </c>
-      <c r="C76" s="114" t="s">
+      <c r="C76" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="D76" s="115" t="e">
+      <c r="D76" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E76" s="115" t="s">
+      <c r="E76" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F76" s="117"/>
+      <c r="F76" s="116"/>
     </row>
     <row r="77" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A77" s="106"/>
-      <c r="B77" s="113" t="s">
+      <c r="A77" s="105"/>
+      <c r="B77" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="C77" s="114" t="s">
+      <c r="C77" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="D77" s="115" t="e">
+      <c r="D77" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E77" s="115" t="s">
+      <c r="E77" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F77" s="117"/>
+      <c r="F77" s="116"/>
     </row>
     <row r="78" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A78" s="106"/>
-      <c r="B78" s="113" t="s">
+      <c r="A78" s="105"/>
+      <c r="B78" s="112" t="s">
         <v>31</v>
       </c>
-      <c r="C78" s="114" t="s">
+      <c r="C78" s="113" t="s">
         <v>32</v>
       </c>
-      <c r="D78" s="115" t="e">
+      <c r="D78" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E78" s="115" t="s">
+      <c r="E78" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F78" s="117"/>
+      <c r="F78" s="116"/>
     </row>
     <row r="79" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A79" s="168"/>
-      <c r="B79" s="113" t="s">
+      <c r="A79" s="172"/>
+      <c r="B79" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="C79" s="114" t="s">
+      <c r="C79" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="D79" s="115" t="e">
+      <c r="D79" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E79" s="115" t="s">
+      <c r="E79" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F79" s="117"/>
+      <c r="F79" s="116"/>
     </row>
     <row r="80" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A80" s="169"/>
-      <c r="B80" s="113" t="s">
+      <c r="A80" s="173"/>
+      <c r="B80" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="C80" s="114" t="s">
+      <c r="C80" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="D80" s="115" t="e">
+      <c r="D80" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E80" s="115" t="s">
+      <c r="E80" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F80" s="117"/>
+      <c r="F80" s="116"/>
     </row>
     <row r="81" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A81" s="169"/>
-      <c r="B81" s="113" t="s">
+      <c r="A81" s="173"/>
+      <c r="B81" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="C81" s="114" t="s">
+      <c r="C81" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="D81" s="115" t="e">
+      <c r="D81" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E81" s="115" t="s">
+      <c r="E81" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F81" s="117"/>
+      <c r="F81" s="116"/>
     </row>
     <row r="82" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A82" s="106"/>
-      <c r="B82" s="113" t="s">
+      <c r="A82" s="105"/>
+      <c r="B82" s="112" t="s">
         <v>38</v>
       </c>
-      <c r="C82" s="114" t="s">
+      <c r="C82" s="113" t="s">
         <v>39</v>
       </c>
-      <c r="D82" s="115" t="e">
+      <c r="D82" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E82" s="115" t="s">
+      <c r="E82" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F82" s="117"/>
+      <c r="F82" s="116"/>
     </row>
     <row r="83" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A83" s="106"/>
-      <c r="B83" s="113" t="s">
+      <c r="A83" s="105"/>
+      <c r="B83" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="C83" s="114" t="s">
+      <c r="C83" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D83" s="115" t="e">
+      <c r="D83" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E83" s="115" t="s">
+      <c r="E83" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F83" s="117"/>
+      <c r="F83" s="116"/>
     </row>
     <row r="84" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A84" s="106"/>
-      <c r="B84" s="113" t="s">
+      <c r="A84" s="105"/>
+      <c r="B84" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="C84" s="114" t="s">
+      <c r="C84" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="D84" s="115" t="e">
+      <c r="D84" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E84" s="115" t="s">
+      <c r="E84" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F84" s="117"/>
+      <c r="F84" s="116"/>
     </row>
     <row r="85" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A85" s="106"/>
-      <c r="B85" s="113" t="s">
+      <c r="A85" s="105"/>
+      <c r="B85" s="112" t="s">
         <v>44</v>
       </c>
-      <c r="C85" s="114" t="s">
+      <c r="C85" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="D85" s="115" t="e">
+      <c r="D85" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E85" s="115" t="s">
+      <c r="E85" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F85" s="117"/>
+      <c r="F85" s="116"/>
     </row>
     <row r="86" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A86" s="106"/>
-      <c r="B86" s="113" t="s">
+      <c r="A86" s="105"/>
+      <c r="B86" s="112" t="s">
         <v>46</v>
       </c>
-      <c r="C86" s="114" t="s">
+      <c r="C86" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="D86" s="115" t="e">
+      <c r="D86" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E86" s="115" t="s">
+      <c r="E86" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F86" s="117"/>
+      <c r="F86" s="116"/>
     </row>
     <row r="87" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A87" s="106"/>
-      <c r="B87" s="113" t="s">
+      <c r="A87" s="105"/>
+      <c r="B87" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="C87" s="114" t="s">
+      <c r="C87" s="113" t="s">
         <v>49</v>
       </c>
-      <c r="D87" s="115" t="e">
+      <c r="D87" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E87" s="115" t="s">
+      <c r="E87" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F87" s="117"/>
+      <c r="F87" s="116"/>
     </row>
     <row r="88" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A88" s="106"/>
-      <c r="B88" s="113" t="s">
+      <c r="A88" s="105"/>
+      <c r="B88" s="112" t="s">
         <v>50</v>
       </c>
-      <c r="C88" s="114" t="s">
+      <c r="C88" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="D88" s="115" t="e">
+      <c r="D88" s="114" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E88" s="115" t="s">
+      <c r="E88" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F88" s="117"/>
+      <c r="F88" s="116"/>
     </row>
     <row r="89" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A89" s="106"/>
-      <c r="B89" s="117"/>
-      <c r="C89" s="124"/>
-      <c r="D89" s="115"/>
-      <c r="E89" s="115"/>
-      <c r="F89" s="117"/>
+      <c r="A89" s="105"/>
+      <c r="B89" s="116"/>
+      <c r="C89" s="123"/>
+      <c r="D89" s="114"/>
+      <c r="E89" s="114"/>
+      <c r="F89" s="116"/>
     </row>
     <row r="90" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A90" s="106"/>
-      <c r="B90" s="117"/>
-      <c r="C90" s="125" t="s">
+      <c r="A90" s="105"/>
+      <c r="B90" s="116"/>
+      <c r="C90" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="D90" s="126"/>
-      <c r="E90" s="126"/>
-      <c r="F90" s="127"/>
+      <c r="D90" s="125"/>
+      <c r="E90" s="125"/>
+      <c r="F90" s="126"/>
     </row>
     <row r="91" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A91" s="106"/>
-      <c r="B91" s="117"/>
-      <c r="C91" s="117"/>
-      <c r="D91" s="117"/>
-      <c r="E91" s="117"/>
-      <c r="F91" s="117"/>
-      <c r="G91" s="106"/>
-      <c r="H91" s="106"/>
+      <c r="A91" s="105"/>
+      <c r="B91" s="116"/>
+      <c r="C91" s="116"/>
+      <c r="D91" s="116"/>
+      <c r="E91" s="116"/>
+      <c r="F91" s="116"/>
+      <c r="G91" s="105"/>
+      <c r="H91" s="105"/>
     </row>
     <row r="92" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A92" s="106"/>
-      <c r="B92" s="117"/>
-      <c r="C92" s="128" t="s">
+      <c r="A92" s="105"/>
+      <c r="B92" s="116"/>
+      <c r="C92" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="D92" s="166" t="e">
+      <c r="D92" s="170" t="e">
         <f>SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="E92" s="167"/>
-      <c r="F92" s="129"/>
-      <c r="G92" s="106"/>
-      <c r="H92" s="106"/>
+      <c r="E92" s="171"/>
+      <c r="F92" s="128"/>
+      <c r="G92" s="105"/>
+      <c r="H92" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4212,76 +4375,76 @@
   <dimension ref="B2:C11"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="4" style="138" customWidth="1"/>
-    <col min="2" max="2" width="36.77734375" style="138" customWidth="1"/>
-    <col min="3" max="3" width="110.5546875" style="138" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="138"/>
+    <col min="1" max="1" width="4" style="137" customWidth="1"/>
+    <col min="2" max="2" width="36.77734375" style="137" customWidth="1"/>
+    <col min="3" max="3" width="110.5546875" style="137" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="137"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="20.399999999999999">
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="136" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="15">
+      <c r="B3" s="138" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="45" customHeight="1">
+      <c r="B5" s="139" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="140" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="30" customHeight="1">
+      <c r="B6" s="139" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="140" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="45" customHeight="1">
+      <c r="B7" s="139" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" ht="15">
-      <c r="B3" s="139" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" ht="45" customHeight="1">
-      <c r="B5" s="140" t="s">
+      <c r="C7" s="140" t="s">
         <v>144</v>
       </c>
-      <c r="C5" s="141" t="s">
+    </row>
+    <row r="8" spans="2:3" ht="60" customHeight="1">
+      <c r="B8" s="139" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" ht="30" customHeight="1">
-      <c r="B6" s="140" t="s">
+      <c r="C8" s="140" t="s">
         <v>146</v>
       </c>
-      <c r="C6" s="141" t="s">
+    </row>
+    <row r="9" spans="2:3" ht="60" customHeight="1">
+      <c r="B9" s="139" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="7" spans="2:3" ht="45" customHeight="1">
-      <c r="B7" s="140" t="s">
+      <c r="C9" s="140" t="s">
         <v>148</v>
       </c>
-      <c r="C7" s="141" t="s">
+    </row>
+    <row r="10" spans="2:3" ht="45" customHeight="1">
+      <c r="B10" s="139" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="8" spans="2:3" ht="60" customHeight="1">
-      <c r="B8" s="140" t="s">
+      <c r="C10" s="140" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="141" t="s">
+    </row>
+    <row r="11" spans="2:3" ht="60" customHeight="1">
+      <c r="B11" s="139" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="9" spans="2:3" ht="60" customHeight="1">
-      <c r="B9" s="140" t="s">
+      <c r="C11" s="140" t="s">
         <v>152</v>
-      </c>
-      <c r="C9" s="141" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="45" customHeight="1">
-      <c r="B10" s="140" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" s="141" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" ht="60" customHeight="1">
-      <c r="B11" s="140" t="s">
-        <v>156</v>
-      </c>
-      <c r="C11" s="141" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -4295,615 +4458,615 @@
   <dimension ref="B2:I35"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="4" style="138" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" style="138" customWidth="1"/>
-    <col min="3" max="3" width="15" style="138" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" style="138" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.21875" style="138" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="138" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" style="138" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.21875" style="138" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.33203125" style="138" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="138"/>
+    <col min="1" max="1" width="4" style="137" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" style="137" customWidth="1"/>
+    <col min="3" max="3" width="15" style="137" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" style="137" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" style="137" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="137" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" style="137" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.21875" style="137" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.33203125" style="137" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="137"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="20.399999999999999">
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="136" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="15">
+      <c r="B3" s="138" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="16.2">
+      <c r="B5" s="141" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="141" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" s="141" t="s">
+        <v>156</v>
+      </c>
+      <c r="E5" s="141" t="s">
+        <v>157</v>
+      </c>
+      <c r="F5" s="141" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="3" spans="2:9" ht="15">
-      <c r="B3" s="139" t="s">
+      <c r="G5" s="141" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="5" spans="2:9" ht="16.2">
-      <c r="B5" s="142" t="s">
+      <c r="H5" s="141" t="s">
         <v>160</v>
       </c>
-      <c r="C5" s="142" t="s">
+      <c r="I5" s="141" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="15.6">
+      <c r="B6" s="142" t="s">
         <v>161</v>
       </c>
-      <c r="D5" s="142" t="s">
+      <c r="C6" s="142">
+        <v>12684</v>
+      </c>
+      <c r="D6" s="142">
+        <v>1.27</v>
+      </c>
+      <c r="E6" s="142" t="s">
         <v>162</v>
       </c>
-      <c r="E5" s="142" t="s">
+      <c r="F6" s="142">
+        <v>25314</v>
+      </c>
+      <c r="G6" s="142">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="H6" s="142" t="s">
+        <v>162</v>
+      </c>
+      <c r="I6" s="140"/>
+    </row>
+    <row r="7" spans="2:9" ht="16.2">
+      <c r="B7" s="147" t="s">
         <v>163</v>
       </c>
-      <c r="F5" s="142" t="s">
+      <c r="C7" s="147">
+        <v>14300</v>
+      </c>
+      <c r="D7" s="147">
+        <v>1.43</v>
+      </c>
+      <c r="E7" s="147" t="s">
         <v>164</v>
       </c>
-      <c r="G5" s="142" t="s">
+      <c r="F7" s="147">
+        <v>32985</v>
+      </c>
+      <c r="G7" s="147">
+        <v>3.3</v>
+      </c>
+      <c r="H7" s="147" t="s">
+        <v>164</v>
+      </c>
+      <c r="I7" s="148" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="15.6">
+      <c r="B8" s="142" t="s">
         <v>165</v>
       </c>
-      <c r="H5" s="142" t="s">
+      <c r="C8" s="142">
+        <v>15679</v>
+      </c>
+      <c r="D8" s="142">
+        <v>1.57</v>
+      </c>
+      <c r="E8" s="142" t="s">
         <v>166</v>
       </c>
-      <c r="I5" s="142" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" ht="15.6">
-      <c r="B6" s="143" t="s">
+      <c r="F8" s="142">
+        <v>38369</v>
+      </c>
+      <c r="G8" s="142">
+        <v>3.84</v>
+      </c>
+      <c r="H8" s="142" t="s">
+        <v>166</v>
+      </c>
+      <c r="I8" s="140"/>
+    </row>
+    <row r="9" spans="2:9" ht="15.6">
+      <c r="B9" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="C6" s="143">
-        <v>15177</v>
-      </c>
-      <c r="D6" s="143">
-        <v>1.52</v>
-      </c>
-      <c r="E6" s="143" t="s">
+      <c r="C9" s="143">
+        <v>16728</v>
+      </c>
+      <c r="D9" s="143">
+        <v>1.67</v>
+      </c>
+      <c r="E9" s="143" t="s">
         <v>168</v>
       </c>
-      <c r="F6" s="143">
-        <v>26195</v>
-      </c>
-      <c r="G6" s="143">
-        <v>2.62</v>
-      </c>
-      <c r="H6" s="143" t="s">
+      <c r="F9" s="143">
+        <v>42525</v>
+      </c>
+      <c r="G9" s="143">
+        <v>4.25</v>
+      </c>
+      <c r="H9" s="143" t="s">
         <v>168</v>
       </c>
-      <c r="I6" s="141"/>
-    </row>
-    <row r="7" spans="2:9" ht="16.2">
-      <c r="B7" s="148" t="s">
+      <c r="I9" s="144"/>
+    </row>
+    <row r="10" spans="2:9" ht="15.6">
+      <c r="B10" s="142" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="148">
-        <v>17513</v>
-      </c>
-      <c r="D7" s="148">
-        <v>1.75</v>
-      </c>
-      <c r="E7" s="148" t="s">
+      <c r="C10" s="142">
+        <v>17704</v>
+      </c>
+      <c r="D10" s="142">
+        <v>1.77</v>
+      </c>
+      <c r="E10" s="142" t="s">
         <v>170</v>
       </c>
-      <c r="F7" s="148">
-        <v>33960</v>
-      </c>
-      <c r="G7" s="148">
-        <v>3.4</v>
-      </c>
-      <c r="H7" s="148" t="s">
+      <c r="F10" s="142">
+        <v>46528</v>
+      </c>
+      <c r="G10" s="142">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H10" s="142" t="s">
         <v>170</v>
       </c>
-      <c r="I7" s="149" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="15.6">
-      <c r="B8" s="143" t="s">
+      <c r="I10" s="140"/>
+    </row>
+    <row r="11" spans="2:9" ht="15.6">
+      <c r="B11" s="143" t="s">
         <v>171</v>
       </c>
-      <c r="C8" s="143">
-        <v>18955</v>
-      </c>
-      <c r="D8" s="143">
-        <v>1.9</v>
-      </c>
-      <c r="E8" s="143" t="s">
+      <c r="C11" s="143">
+        <v>18582</v>
+      </c>
+      <c r="D11" s="143">
+        <v>1.86</v>
+      </c>
+      <c r="E11" s="143" t="s">
         <v>172</v>
       </c>
-      <c r="F8" s="143">
-        <v>39920</v>
-      </c>
-      <c r="G8" s="143">
-        <v>3.99</v>
-      </c>
-      <c r="H8" s="143" t="s">
+      <c r="F11" s="143">
+        <v>50155</v>
+      </c>
+      <c r="G11" s="143">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="H11" s="143" t="s">
         <v>172</v>
       </c>
-      <c r="I8" s="141"/>
-    </row>
-    <row r="9" spans="2:9" ht="15.6">
-      <c r="B9" s="144" t="s">
+      <c r="I11" s="144"/>
+    </row>
+    <row r="12" spans="2:9" ht="15.6">
+      <c r="B12" s="142" t="s">
         <v>173</v>
       </c>
-      <c r="C9" s="144">
-        <v>20174</v>
-      </c>
-      <c r="D9" s="144">
-        <v>2.02</v>
-      </c>
-      <c r="E9" s="144" t="s">
+      <c r="C12" s="142">
+        <v>19408</v>
+      </c>
+      <c r="D12" s="142">
+        <v>1.94</v>
+      </c>
+      <c r="E12" s="142" t="s">
         <v>174</v>
       </c>
-      <c r="F9" s="144">
-        <v>45695</v>
-      </c>
-      <c r="G9" s="144">
-        <v>4.57</v>
-      </c>
-      <c r="H9" s="144" t="s">
+      <c r="F12" s="142">
+        <v>53609</v>
+      </c>
+      <c r="G12" s="142">
+        <v>5.36</v>
+      </c>
+      <c r="H12" s="142" t="s">
         <v>174</v>
       </c>
-      <c r="I9" s="145"/>
-    </row>
-    <row r="10" spans="2:9" ht="15.6">
-      <c r="B10" s="143" t="s">
+      <c r="I12" s="140"/>
+    </row>
+    <row r="13" spans="2:9" ht="15.6">
+      <c r="B13" s="143" t="s">
         <v>175</v>
       </c>
-      <c r="C10" s="143">
-        <v>21295</v>
-      </c>
-      <c r="D10" s="143">
-        <v>2.13</v>
-      </c>
-      <c r="E10" s="143" t="s">
+      <c r="C13" s="143">
+        <v>20300</v>
+      </c>
+      <c r="D13" s="143">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="E13" s="143" t="s">
         <v>176</v>
       </c>
-      <c r="F10" s="143">
-        <v>50237</v>
-      </c>
-      <c r="G10" s="143">
-        <v>5.0199999999999996</v>
-      </c>
-      <c r="H10" s="143" t="s">
+      <c r="F13" s="143">
+        <v>56728</v>
+      </c>
+      <c r="G13" s="143">
+        <v>5.67</v>
+      </c>
+      <c r="H13" s="143" t="s">
         <v>176</v>
       </c>
-      <c r="I10" s="141"/>
-    </row>
-    <row r="11" spans="2:9" ht="15.6">
-      <c r="B11" s="144" t="s">
+      <c r="I13" s="144"/>
+    </row>
+    <row r="14" spans="2:9" ht="15.6">
+      <c r="B14" s="142" t="s">
         <v>177</v>
       </c>
-      <c r="C11" s="144">
-        <v>22433</v>
-      </c>
-      <c r="D11" s="144">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="E11" s="144" t="s">
+      <c r="C14" s="142">
+        <v>21139</v>
+      </c>
+      <c r="D14" s="142">
+        <v>2.11</v>
+      </c>
+      <c r="E14" s="142" t="s">
         <v>178</v>
       </c>
-      <c r="F11" s="144">
-        <v>54747</v>
-      </c>
-      <c r="G11" s="144">
-        <v>5.47</v>
-      </c>
-      <c r="H11" s="144" t="s">
+      <c r="F14" s="142">
+        <v>59881</v>
+      </c>
+      <c r="G14" s="142">
+        <v>5.99</v>
+      </c>
+      <c r="H14" s="142" t="s">
         <v>178</v>
       </c>
-      <c r="I11" s="145"/>
-    </row>
-    <row r="12" spans="2:9" ht="15.6">
-      <c r="B12" s="143" t="s">
+      <c r="I14" s="140"/>
+    </row>
+    <row r="15" spans="2:9" ht="16.2">
+      <c r="B15" s="147" t="s">
         <v>179</v>
       </c>
-      <c r="C12" s="143">
-        <v>23404</v>
-      </c>
-      <c r="D12" s="143">
-        <v>2.34</v>
-      </c>
-      <c r="E12" s="143" t="s">
+      <c r="C15" s="147">
+        <v>22009</v>
+      </c>
+      <c r="D15" s="147">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E15" s="147" t="s">
         <v>180</v>
       </c>
-      <c r="F12" s="143">
-        <v>59297</v>
-      </c>
-      <c r="G12" s="143">
-        <v>5.93</v>
-      </c>
-      <c r="H12" s="143" t="s">
+      <c r="F15" s="147">
+        <v>63130</v>
+      </c>
+      <c r="G15" s="147">
+        <v>6.31</v>
+      </c>
+      <c r="H15" s="147" t="s">
         <v>180</v>
       </c>
-      <c r="I12" s="141"/>
-    </row>
-    <row r="13" spans="2:9" ht="15.6">
-      <c r="B13" s="144" t="s">
+      <c r="I15" s="148" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="15.6">
+      <c r="B16" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="144">
-        <v>24347</v>
-      </c>
-      <c r="D13" s="144">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="E13" s="144" t="s">
+      <c r="C16" s="142">
+        <v>22905</v>
+      </c>
+      <c r="D16" s="142">
+        <v>2.29</v>
+      </c>
+      <c r="E16" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="F13" s="144">
-        <v>63309</v>
-      </c>
-      <c r="G13" s="144">
-        <v>6.33</v>
-      </c>
-      <c r="H13" s="144" t="s">
+      <c r="F16" s="142">
+        <v>66642</v>
+      </c>
+      <c r="G16" s="142">
+        <v>6.66</v>
+      </c>
+      <c r="H16" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I13" s="145"/>
-    </row>
-    <row r="14" spans="2:9" ht="15.6">
-      <c r="B14" s="143" t="s">
+      <c r="I16" s="140"/>
+    </row>
+    <row r="17" spans="2:9" ht="15.6">
+      <c r="B17" s="143" t="s">
         <v>183</v>
       </c>
-      <c r="C14" s="143">
-        <v>25370</v>
-      </c>
-      <c r="D14" s="143">
-        <v>2.54</v>
-      </c>
-      <c r="E14" s="143" t="s">
+      <c r="C17" s="143">
+        <v>23827</v>
+      </c>
+      <c r="D17" s="143">
+        <v>2.38</v>
+      </c>
+      <c r="E17" s="143" t="s">
         <v>184</v>
       </c>
-      <c r="F14" s="143">
-        <v>67487</v>
-      </c>
-      <c r="G14" s="143">
-        <v>6.75</v>
-      </c>
-      <c r="H14" s="143" t="s">
+      <c r="F17" s="143">
+        <v>70036</v>
+      </c>
+      <c r="G17" s="143">
+        <v>7</v>
+      </c>
+      <c r="H17" s="143" t="s">
         <v>184</v>
       </c>
-      <c r="I14" s="141"/>
-    </row>
-    <row r="15" spans="2:9" ht="16.2">
-      <c r="B15" s="148" t="s">
+      <c r="I17" s="144"/>
+    </row>
+    <row r="18" spans="2:9" ht="15.6">
+      <c r="B18" s="142" t="s">
         <v>185</v>
       </c>
-      <c r="C15" s="148">
-        <v>26348</v>
-      </c>
-      <c r="D15" s="148">
-        <v>2.63</v>
-      </c>
-      <c r="E15" s="148" t="s">
+      <c r="C18" s="142">
+        <v>24744</v>
+      </c>
+      <c r="D18" s="142">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="E18" s="142" t="s">
         <v>186</v>
       </c>
-      <c r="F15" s="148">
-        <v>71179</v>
-      </c>
-      <c r="G15" s="148">
-        <v>7.12</v>
-      </c>
-      <c r="H15" s="148" t="s">
+      <c r="F18" s="142">
+        <v>74037</v>
+      </c>
+      <c r="G18" s="142">
+        <v>7.4</v>
+      </c>
+      <c r="H18" s="142" t="s">
         <v>186</v>
       </c>
-      <c r="I15" s="149" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" ht="15.6">
-      <c r="B16" s="143" t="s">
+      <c r="I18" s="140"/>
+    </row>
+    <row r="19" spans="2:9" ht="15.6">
+      <c r="B19" s="143" t="s">
         <v>187</v>
       </c>
-      <c r="C16" s="143">
-        <v>27400</v>
-      </c>
-      <c r="D16" s="143">
-        <v>2.74</v>
-      </c>
-      <c r="E16" s="143" t="s">
+      <c r="C19" s="143">
+        <v>25874</v>
+      </c>
+      <c r="D19" s="143">
+        <v>2.59</v>
+      </c>
+      <c r="E19" s="143" t="s">
         <v>188</v>
       </c>
-      <c r="F16" s="143">
-        <v>75381</v>
-      </c>
-      <c r="G16" s="143">
-        <v>7.54</v>
-      </c>
-      <c r="H16" s="143" t="s">
+      <c r="F19" s="143">
+        <v>78392</v>
+      </c>
+      <c r="G19" s="143">
+        <v>7.84</v>
+      </c>
+      <c r="H19" s="143" t="s">
         <v>188</v>
       </c>
-      <c r="I16" s="141"/>
-    </row>
-    <row r="17" spans="2:9" ht="15.6">
-      <c r="B17" s="144" t="s">
+      <c r="I19" s="144"/>
+    </row>
+    <row r="20" spans="2:9" ht="15.6">
+      <c r="B20" s="142" t="s">
         <v>189</v>
       </c>
-      <c r="C17" s="144">
-        <v>28444</v>
-      </c>
-      <c r="D17" s="144">
-        <v>2.84</v>
-      </c>
-      <c r="E17" s="144" t="s">
+      <c r="C20" s="142">
+        <v>26996</v>
+      </c>
+      <c r="D20" s="142">
+        <v>2.7</v>
+      </c>
+      <c r="E20" s="142" t="s">
         <v>190</v>
       </c>
-      <c r="F17" s="144">
-        <v>79280</v>
-      </c>
-      <c r="G17" s="144">
-        <v>7.93</v>
-      </c>
-      <c r="H17" s="144" t="s">
+      <c r="F20" s="142">
+        <v>82997</v>
+      </c>
+      <c r="G20" s="142">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="H20" s="142" t="s">
         <v>190</v>
       </c>
-      <c r="I17" s="145"/>
-    </row>
-    <row r="18" spans="2:9" ht="15.6">
-      <c r="B18" s="143" t="s">
+      <c r="I20" s="140"/>
+    </row>
+    <row r="21" spans="2:9" ht="15.6">
+      <c r="B21" s="143" t="s">
         <v>191</v>
       </c>
-      <c r="C18" s="143">
-        <v>29531</v>
-      </c>
-      <c r="D18" s="143">
-        <v>2.95</v>
-      </c>
-      <c r="E18" s="143" t="s">
+      <c r="C21" s="143">
+        <v>28337</v>
+      </c>
+      <c r="D21" s="143">
+        <v>2.83</v>
+      </c>
+      <c r="E21" s="143" t="s">
         <v>192</v>
       </c>
-      <c r="F18" s="143">
-        <v>84128</v>
-      </c>
-      <c r="G18" s="143">
-        <v>8.41</v>
-      </c>
-      <c r="H18" s="143" t="s">
+      <c r="F21" s="143">
+        <v>88338</v>
+      </c>
+      <c r="G21" s="143">
+        <v>8.83</v>
+      </c>
+      <c r="H21" s="143" t="s">
         <v>192</v>
       </c>
-      <c r="I18" s="141"/>
-    </row>
-    <row r="19" spans="2:9" ht="15.6">
-      <c r="B19" s="144" t="s">
+      <c r="I21" s="144"/>
+    </row>
+    <row r="22" spans="2:9" ht="15.6">
+      <c r="B22" s="142" t="s">
         <v>193</v>
       </c>
-      <c r="C19" s="144">
-        <v>30724</v>
-      </c>
-      <c r="D19" s="144">
-        <v>3.07</v>
-      </c>
-      <c r="E19" s="144" t="s">
+      <c r="C22" s="142">
+        <v>29861</v>
+      </c>
+      <c r="D22" s="142">
+        <v>2.99</v>
+      </c>
+      <c r="E22" s="142" t="s">
         <v>194</v>
       </c>
-      <c r="F19" s="144">
-        <v>89356</v>
-      </c>
-      <c r="G19" s="144">
-        <v>8.94</v>
-      </c>
-      <c r="H19" s="144" t="s">
+      <c r="F22" s="142">
+        <v>95003</v>
+      </c>
+      <c r="G22" s="142">
+        <v>9.5</v>
+      </c>
+      <c r="H22" s="142" t="s">
         <v>194</v>
       </c>
-      <c r="I19" s="145"/>
-    </row>
-    <row r="20" spans="2:9" ht="15.6">
-      <c r="B20" s="143" t="s">
+      <c r="I22" s="140"/>
+    </row>
+    <row r="23" spans="2:9" ht="16.2">
+      <c r="B23" s="147" t="s">
         <v>195</v>
       </c>
-      <c r="C20" s="143">
-        <v>32002</v>
-      </c>
-      <c r="D20" s="143">
-        <v>3.2</v>
-      </c>
-      <c r="E20" s="143" t="s">
+      <c r="C23" s="147">
+        <v>32139</v>
+      </c>
+      <c r="D23" s="147">
+        <v>3.21</v>
+      </c>
+      <c r="E23" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="F20" s="143">
-        <v>94393</v>
-      </c>
-      <c r="G20" s="143">
-        <v>9.44</v>
-      </c>
-      <c r="H20" s="143" t="s">
+      <c r="F23" s="147">
+        <v>103850</v>
+      </c>
+      <c r="G23" s="147">
+        <v>10.39</v>
+      </c>
+      <c r="H23" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="I20" s="141"/>
-    </row>
-    <row r="21" spans="2:9" ht="15.6">
-      <c r="B21" s="144" t="s">
+      <c r="I23" s="148" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="15.6">
+      <c r="B24" s="142" t="s">
         <v>197</v>
       </c>
-      <c r="C21" s="144">
-        <v>33510</v>
-      </c>
-      <c r="D21" s="144">
-        <v>3.35</v>
-      </c>
-      <c r="E21" s="144" t="s">
+      <c r="C24" s="142">
+        <v>35600</v>
+      </c>
+      <c r="D24" s="142">
+        <v>3.56</v>
+      </c>
+      <c r="E24" s="142" t="s">
         <v>198</v>
       </c>
-      <c r="F21" s="144">
-        <v>101082</v>
-      </c>
-      <c r="G21" s="144">
-        <v>10.11</v>
-      </c>
-      <c r="H21" s="144" t="s">
+      <c r="F24" s="142">
+        <v>119747</v>
+      </c>
+      <c r="G24" s="142">
+        <v>11.97</v>
+      </c>
+      <c r="H24" s="142" t="s">
         <v>198</v>
       </c>
-      <c r="I21" s="145"/>
-    </row>
-    <row r="22" spans="2:9" ht="15.6">
-      <c r="B22" s="143" t="s">
+      <c r="I24" s="140"/>
+    </row>
+    <row r="26" spans="2:9" ht="17.399999999999999">
+      <c r="B26" s="145" t="s">
         <v>199</v>
       </c>
-      <c r="C22" s="143">
-        <v>35268</v>
-      </c>
-      <c r="D22" s="143">
-        <v>3.53</v>
-      </c>
-      <c r="E22" s="143" t="s">
+    </row>
+    <row r="27" spans="2:9" ht="16.2">
+      <c r="B27" s="180" t="s">
         <v>200</v>
       </c>
-      <c r="F22" s="143">
-        <v>109495</v>
-      </c>
-      <c r="G22" s="143">
-        <v>10.95</v>
-      </c>
-      <c r="H22" s="143" t="s">
-        <v>200</v>
-      </c>
-      <c r="I22" s="141"/>
-    </row>
-    <row r="23" spans="2:9" ht="16.2">
-      <c r="B23" s="148" t="s">
+      <c r="C27" s="181"/>
+      <c r="D27" s="182"/>
+      <c r="E27" s="141" t="s">
         <v>201</v>
       </c>
-      <c r="C23" s="148">
-        <v>37643</v>
-      </c>
-      <c r="D23" s="148">
-        <v>3.76</v>
-      </c>
-      <c r="E23" s="148" t="s">
+      <c r="F27" s="141" t="s">
         <v>202</v>
       </c>
-      <c r="F23" s="148">
-        <v>119858</v>
-      </c>
-      <c r="G23" s="148">
-        <v>11.99</v>
-      </c>
-      <c r="H23" s="148" t="s">
-        <v>202</v>
-      </c>
-      <c r="I23" s="149" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" ht="15.6">
-      <c r="B24" s="143" t="s">
-        <v>203</v>
-      </c>
-      <c r="C24" s="143">
-        <v>41555</v>
-      </c>
-      <c r="D24" s="143">
-        <v>4.16</v>
-      </c>
-      <c r="E24" s="143" t="s">
-        <v>204</v>
-      </c>
-      <c r="F24" s="143">
-        <v>134992</v>
-      </c>
-      <c r="G24" s="143">
-        <v>13.5</v>
-      </c>
-      <c r="H24" s="143" t="s">
-        <v>204</v>
-      </c>
-      <c r="I24" s="141"/>
-    </row>
-    <row r="26" spans="2:9" ht="17.399999999999999">
-      <c r="B26" s="146" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" ht="16.2">
-      <c r="B27" s="170" t="s">
+    </row>
+    <row r="28" spans="2:9" ht="16.2" customHeight="1">
+      <c r="B28" s="174" t="s">
+        <v>220</v>
+      </c>
+      <c r="C28" s="175"/>
+      <c r="D28" s="176"/>
+      <c r="E28" s="149">
+        <v>0.9</v>
+      </c>
+      <c r="F28" s="149">
+        <v>0.98899999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" ht="16.2" customHeight="1">
+      <c r="B29" s="177" t="s">
+        <v>221</v>
+      </c>
+      <c r="C29" s="178"/>
+      <c r="D29" s="179"/>
+      <c r="E29" s="150">
+        <v>0.5</v>
+      </c>
+      <c r="F29" s="150">
+        <v>0.96399999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" ht="16.2" customHeight="1">
+      <c r="B30" s="174" t="s">
+        <v>222</v>
+      </c>
+      <c r="C30" s="175"/>
+      <c r="D30" s="176"/>
+      <c r="E30" s="149">
+        <v>0.1</v>
+      </c>
+      <c r="F30" s="149">
+        <v>0.90700000000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" ht="15.6">
+      <c r="B31" s="177" t="s">
         <v>206</v>
       </c>
-      <c r="C27" s="171"/>
-      <c r="D27" s="172"/>
-      <c r="E27" s="142" t="s">
+      <c r="C31" s="178"/>
+      <c r="D31" s="179"/>
+      <c r="E31" s="161">
+        <v>1E-3</v>
+      </c>
+      <c r="F31" s="151">
+        <v>0.70299999999999996</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" ht="15.6" customHeight="1">
+      <c r="B32" s="174" t="s">
         <v>207</v>
       </c>
-      <c r="F27" s="142" t="s">
+      <c r="C32" s="175"/>
+      <c r="D32" s="176"/>
+      <c r="E32" s="152">
+        <v>0</v>
+      </c>
+      <c r="F32" s="152">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" ht="15.6" customHeight="1">
+      <c r="B33" s="177" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="28" spans="2:9" ht="16.2" customHeight="1">
-      <c r="B28" s="173" t="s">
-        <v>216</v>
-      </c>
-      <c r="C28" s="174"/>
-      <c r="D28" s="175"/>
-      <c r="E28" s="150">
-        <v>0.9</v>
-      </c>
-      <c r="F28" s="150">
-        <v>0.98199999999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" ht="16.2" customHeight="1">
-      <c r="B29" s="176" t="s">
-        <v>217</v>
-      </c>
-      <c r="C29" s="177"/>
-      <c r="D29" s="178"/>
-      <c r="E29" s="151">
-        <v>0.5</v>
-      </c>
-      <c r="F29" s="151">
-        <v>0.94899999999999995</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" ht="16.2" customHeight="1">
-      <c r="B30" s="173" t="s">
-        <v>218</v>
-      </c>
-      <c r="C30" s="174"/>
-      <c r="D30" s="175"/>
-      <c r="E30" s="150">
-        <v>0.1</v>
-      </c>
-      <c r="F30" s="150">
-        <v>0.871</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" ht="15.6">
-      <c r="B31" s="176" t="s">
-        <v>219</v>
-      </c>
-      <c r="C31" s="177"/>
-      <c r="D31" s="178"/>
-      <c r="E31" s="152">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="F31" s="152">
-        <v>0.752</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" ht="15.6" customHeight="1">
-      <c r="B32" s="173" t="s">
-        <v>220</v>
-      </c>
-      <c r="C32" s="174"/>
-      <c r="D32" s="175"/>
-      <c r="E32" s="153" t="s">
-        <v>209</v>
-      </c>
-      <c r="F32" s="153">
-        <v>0.20899999999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" ht="15.6" customHeight="1">
-      <c r="B33" s="176" t="s">
-        <v>221</v>
-      </c>
-      <c r="C33" s="177"/>
-      <c r="D33" s="178"/>
-      <c r="E33" s="152" t="s">
-        <v>209</v>
-      </c>
-      <c r="F33" s="152">
+      <c r="C33" s="178"/>
+      <c r="D33" s="179"/>
+      <c r="E33" s="151">
+        <v>0</v>
+      </c>
+      <c r="F33" s="151">
         <v>2E-3</v>
       </c>
     </row>
     <row r="35" spans="2:6" ht="14.4">
-      <c r="B35" s="147" t="s">
-        <v>222</v>
+      <c r="B35" s="146" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -4926,273 +5089,273 @@
   <dimension ref="B1:H23"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" style="80" customWidth="1"/>
-    <col min="2" max="2" width="7.21875" style="80" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="80" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="80" customWidth="1"/>
-    <col min="5" max="5" width="58.21875" style="80" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="50.77734375" style="80" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="80" customWidth="1"/>
-    <col min="8" max="9" width="9.77734375" style="80" customWidth="1"/>
-    <col min="10" max="10" width="47.5546875" style="80" customWidth="1"/>
-    <col min="11" max="11" width="4.77734375" style="80" customWidth="1"/>
-    <col min="12" max="13" width="7.21875" style="80" customWidth="1"/>
-    <col min="14" max="14" width="8.6640625" style="80" customWidth="1"/>
-    <col min="15" max="15" width="45.44140625" style="80" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="80"/>
+    <col min="1" max="1" width="4.77734375" style="79" customWidth="1"/>
+    <col min="2" max="2" width="7.21875" style="79" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="79" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" style="79" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" style="79" customWidth="1"/>
+    <col min="6" max="6" width="50.77734375" style="79" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="79" customWidth="1"/>
+    <col min="8" max="9" width="9.77734375" style="79" customWidth="1"/>
+    <col min="10" max="10" width="47.5546875" style="79" customWidth="1"/>
+    <col min="11" max="11" width="4.77734375" style="79" customWidth="1"/>
+    <col min="12" max="13" width="7.21875" style="79" customWidth="1"/>
+    <col min="14" max="14" width="8.6640625" style="79" customWidth="1"/>
+    <col min="15" max="15" width="45.44140625" style="79" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="79"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15.6" thickBot="1"/>
     <row r="2" spans="2:8" ht="15.6">
-      <c r="B2" s="87"/>
-      <c r="C2" s="182" t="s">
-        <v>134</v>
-      </c>
-      <c r="D2" s="183"/>
-      <c r="E2" s="184"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="186" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" s="187"/>
+      <c r="E2" s="188"/>
     </row>
     <row r="3" spans="2:8" ht="15.6">
-      <c r="B3" s="88"/>
-      <c r="C3" s="89" t="s">
+      <c r="B3" s="87"/>
+      <c r="C3" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="88" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="89" t="s">
-        <v>131</v>
-      </c>
-      <c r="E3" s="90" t="s">
+      <c r="E3" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="87" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
-    </row>
-    <row r="4" spans="2:8">
-      <c r="B4" s="88" t="s">
+      <c r="C4" s="91">
+        <f>D4*12</f>
+        <v>21600</v>
+      </c>
+      <c r="D4" s="91">
+        <v>1800</v>
+      </c>
+      <c r="E4" s="184" t="s">
+        <v>212</v>
+      </c>
+      <c r="F4" s="183"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="92"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="87" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="92">
-        <f>D4*12</f>
-        <v>26400</v>
-      </c>
-      <c r="D4" s="92">
-        <v>2200</v>
-      </c>
-      <c r="E4" s="180" t="s">
-        <v>140</v>
-      </c>
-      <c r="F4" s="179"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-    </row>
-    <row r="5" spans="2:8">
-      <c r="B5" s="88" t="s">
+      <c r="C5" s="91">
+        <f t="shared" ref="C5:C6" si="0">D5*12</f>
+        <v>21600</v>
+      </c>
+      <c r="D5" s="91">
+        <v>1800</v>
+      </c>
+      <c r="E5" s="185"/>
+      <c r="F5" s="183"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="92">
-        <f t="shared" ref="C5:C6" si="0">D5*12</f>
-        <v>26400</v>
-      </c>
-      <c r="D5" s="92">
-        <v>2200</v>
-      </c>
-      <c r="E5" s="181"/>
-      <c r="F5" s="179"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-    </row>
-    <row r="6" spans="2:8">
-      <c r="B6" s="88" t="s">
+      <c r="C6" s="91">
+        <f t="shared" si="0"/>
+        <v>21600</v>
+      </c>
+      <c r="D6" s="91">
+        <v>1800</v>
+      </c>
+      <c r="E6" s="185"/>
+      <c r="F6" s="183"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+    </row>
+    <row r="7" spans="2:8" ht="15.6" thickBot="1">
+      <c r="B7" s="93" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="92">
-        <f t="shared" si="0"/>
-        <v>26400</v>
-      </c>
-      <c r="D6" s="92">
-        <v>2200</v>
-      </c>
-      <c r="E6" s="181"/>
-      <c r="F6" s="179"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-    </row>
-    <row r="7" spans="2:8" ht="15.6" thickBot="1">
-      <c r="B7" s="94" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="95">
+      <c r="C7" s="94">
         <f>SUM(C4:C6)</f>
-        <v>79200</v>
-      </c>
-      <c r="D7" s="95"/>
-      <c r="E7" s="96"/>
+        <v>64800</v>
+      </c>
+      <c r="D7" s="94"/>
+      <c r="E7" s="95"/>
     </row>
     <row r="9" spans="2:8" ht="15.6" thickBot="1"/>
     <row r="10" spans="2:8" ht="15.6">
-      <c r="B10" s="87"/>
-      <c r="C10" s="182" t="s">
-        <v>132</v>
-      </c>
-      <c r="D10" s="183"/>
-      <c r="E10" s="184"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="186" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="187"/>
+      <c r="E10" s="188"/>
     </row>
     <row r="11" spans="2:8" ht="15.6">
-      <c r="B11" s="97"/>
-      <c r="C11" s="89" t="s">
+      <c r="B11" s="96"/>
+      <c r="C11" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="88" t="s">
         <v>130</v>
       </c>
-      <c r="D11" s="89" t="s">
-        <v>131</v>
-      </c>
-      <c r="E11" s="98" t="s">
+      <c r="E11" s="97" t="s">
+        <v>215</v>
+      </c>
+      <c r="G11" s="90"/>
+      <c r="H11" s="90"/>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="B12" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="91"/>
-      <c r="H11" s="91"/>
-    </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="99" t="s">
+      <c r="C12" s="91">
+        <f>D12*12</f>
+        <v>32400</v>
+      </c>
+      <c r="D12" s="91">
+        <v>2700</v>
+      </c>
+      <c r="E12" s="184" t="s">
+        <v>214</v>
+      </c>
+      <c r="F12" s="183"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="92"/>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" s="96" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="92">
-        <f>D12*12</f>
-        <v>37200</v>
-      </c>
-      <c r="D12" s="92">
-        <v>3100</v>
-      </c>
-      <c r="E12" s="180" t="s">
-        <v>141</v>
-      </c>
-      <c r="F12" s="179"/>
-      <c r="G12" s="100"/>
-      <c r="H12" s="93"/>
-    </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="97" t="s">
+      <c r="C13" s="91">
+        <f t="shared" ref="C13:C14" si="1">D13*12</f>
+        <v>32400</v>
+      </c>
+      <c r="D13" s="91">
+        <v>2700</v>
+      </c>
+      <c r="E13" s="185"/>
+      <c r="F13" s="183"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="92"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="92">
-        <f t="shared" ref="C13:C14" si="1">D13*12</f>
-        <v>37200</v>
-      </c>
-      <c r="D13" s="92">
-        <v>3100</v>
-      </c>
-      <c r="E13" s="181"/>
-      <c r="F13" s="179"/>
-      <c r="G13" s="100"/>
-      <c r="H13" s="93"/>
-    </row>
-    <row r="14" spans="2:8">
-      <c r="B14" s="99" t="s">
+      <c r="C14" s="91">
+        <f t="shared" si="1"/>
+        <v>32400</v>
+      </c>
+      <c r="D14" s="91">
+        <v>2700</v>
+      </c>
+      <c r="E14" s="185"/>
+      <c r="F14" s="183"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="92"/>
+    </row>
+    <row r="15" spans="2:8" ht="15.6" thickBot="1">
+      <c r="B15" s="100" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="92">
-        <f t="shared" si="1"/>
-        <v>37200</v>
-      </c>
-      <c r="D14" s="92">
-        <v>3100</v>
-      </c>
-      <c r="E14" s="181"/>
-      <c r="F14" s="179"/>
-      <c r="G14" s="100"/>
-      <c r="H14" s="93"/>
-    </row>
-    <row r="15" spans="2:8" ht="15.6" thickBot="1">
-      <c r="B15" s="101" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="95">
+      <c r="C15" s="94">
         <f>SUM(C12:C14)</f>
-        <v>111600</v>
-      </c>
-      <c r="D15" s="102"/>
-      <c r="E15" s="103"/>
+        <v>97200</v>
+      </c>
+      <c r="D15" s="101"/>
+      <c r="E15" s="102"/>
     </row>
     <row r="17" spans="2:8" ht="15.6" thickBot="1"/>
     <row r="18" spans="2:8" ht="15.6">
-      <c r="B18" s="87"/>
-      <c r="C18" s="182" t="s">
-        <v>133</v>
-      </c>
-      <c r="D18" s="183"/>
-      <c r="E18" s="184"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="186" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="187"/>
+      <c r="E18" s="188"/>
     </row>
     <row r="19" spans="2:8" ht="15.6">
-      <c r="B19" s="88"/>
-      <c r="C19" s="89" t="s">
+      <c r="B19" s="87"/>
+      <c r="C19" s="88" t="s">
+        <v>129</v>
+      </c>
+      <c r="D19" s="88" t="s">
         <v>130</v>
       </c>
-      <c r="D19" s="89" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19" s="104" t="s">
+      <c r="E19" s="103" t="s">
+        <v>215</v>
+      </c>
+      <c r="G19" s="90"/>
+      <c r="H19" s="90"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="87" t="s">
         <v>56</v>
       </c>
-      <c r="G19" s="91"/>
-      <c r="H19" s="91"/>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="88" t="s">
+      <c r="C20" s="91">
+        <f>D20*12</f>
+        <v>14400</v>
+      </c>
+      <c r="D20" s="91">
+        <v>1200</v>
+      </c>
+      <c r="E20" s="184" t="s">
+        <v>213</v>
+      </c>
+      <c r="F20" s="183"/>
+      <c r="G20" s="99"/>
+      <c r="H20" s="92"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="87" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="92">
-        <f>D20*12</f>
-        <v>16800</v>
-      </c>
-      <c r="D20" s="92">
-        <v>1400</v>
-      </c>
-      <c r="E20" s="180" t="s">
-        <v>142</v>
-      </c>
-      <c r="F20" s="179"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="93"/>
-    </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="88" t="s">
+      <c r="C21" s="91">
+        <f t="shared" ref="C21:C22" si="2">D21*12</f>
+        <v>14400</v>
+      </c>
+      <c r="D21" s="91">
+        <v>1200</v>
+      </c>
+      <c r="E21" s="185"/>
+      <c r="F21" s="183"/>
+      <c r="G21" s="99"/>
+      <c r="H21" s="92"/>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="92">
-        <f t="shared" ref="C21:C22" si="2">D21*12</f>
-        <v>16800</v>
-      </c>
-      <c r="D21" s="92">
-        <v>1400</v>
-      </c>
-      <c r="E21" s="181"/>
-      <c r="F21" s="179"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="93"/>
-    </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="88" t="s">
+      <c r="C22" s="91">
+        <f t="shared" si="2"/>
+        <v>14400</v>
+      </c>
+      <c r="D22" s="91">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="185"/>
+      <c r="F22" s="183"/>
+      <c r="G22" s="99"/>
+      <c r="H22" s="92"/>
+    </row>
+    <row r="23" spans="2:8" ht="15.6" thickBot="1">
+      <c r="B23" s="93" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="92">
-        <f t="shared" si="2"/>
-        <v>16800</v>
-      </c>
-      <c r="D22" s="92">
-        <v>1400</v>
-      </c>
-      <c r="E22" s="181"/>
-      <c r="F22" s="179"/>
-      <c r="G22" s="100"/>
-      <c r="H22" s="93"/>
-    </row>
-    <row r="23" spans="2:8" ht="15.6" thickBot="1">
-      <c r="B23" s="94" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="95">
+      <c r="C23" s="94">
         <f>SUM(C20:C22)</f>
-        <v>50400</v>
-      </c>
-      <c r="D23" s="95"/>
-      <c r="E23" s="103"/>
+        <v>43200</v>
+      </c>
+      <c r="D23" s="94"/>
+      <c r="E23" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -5216,105 +5379,105 @@
   <dimension ref="B1:F10"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="80"/>
-    <col min="2" max="2" width="25.5546875" style="80" customWidth="1"/>
-    <col min="3" max="4" width="13.109375" style="80" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="80"/>
-    <col min="6" max="6" width="13.6640625" style="80" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="80"/>
+    <col min="1" max="1" width="8.88671875" style="79"/>
+    <col min="2" max="2" width="25.5546875" style="79" customWidth="1"/>
+    <col min="3" max="4" width="13.109375" style="79" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="79"/>
+    <col min="6" max="6" width="13.6640625" style="79" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="79"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="15.6" thickBot="1">
-      <c r="C1" s="81"/>
-      <c r="D1" s="82"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="81"/>
     </row>
     <row r="2" spans="2:6" ht="15.6">
-      <c r="C2" s="162" t="s">
-        <v>226</v>
-      </c>
-      <c r="D2" s="163"/>
-      <c r="F2" s="158" t="s">
-        <v>227</v>
+      <c r="C2" s="189" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2" s="190"/>
+      <c r="F2" s="157" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="16.2" thickBot="1">
-      <c r="B3" s="83" t="s">
-        <v>135</v>
-      </c>
-      <c r="C3" s="157">
+      <c r="B3" s="82" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="156">
         <v>599</v>
       </c>
-      <c r="D3" s="84">
+      <c r="D3" s="83">
         <f t="shared" ref="D3" si="0">C3/1.13</f>
         <v>530.08849557522126</v>
       </c>
-      <c r="F3" s="159">
+      <c r="F3" s="158">
         <v>250</v>
       </c>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="83" t="s">
-        <v>210</v>
-      </c>
-      <c r="C4" s="85">
+      <c r="B4" s="82" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" s="84">
         <v>0.65</v>
       </c>
-      <c r="D4" s="84"/>
+      <c r="D4" s="83"/>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="83" t="s">
-        <v>211</v>
-      </c>
-      <c r="C5" s="85">
+      <c r="B5" s="82" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="84">
         <v>0.85</v>
       </c>
-      <c r="D5" s="84"/>
+      <c r="D5" s="83"/>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="82" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="84">
+        <v>0.3</v>
+      </c>
+      <c r="D6" s="85"/>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="85">
-        <v>0.3</v>
-      </c>
-      <c r="D6" s="86"/>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="83" t="s">
+      <c r="C7" s="84">
+        <v>0.75</v>
+      </c>
+      <c r="D7" s="85"/>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="85">
-        <v>0.75</v>
-      </c>
-      <c r="D7" s="86"/>
-    </row>
-    <row r="8" spans="2:6">
-      <c r="B8" s="83" t="s">
+      <c r="C8" s="84">
+        <v>0.05</v>
+      </c>
+      <c r="D8" s="85"/>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="85">
-        <v>0.05</v>
-      </c>
-      <c r="D8" s="86"/>
-    </row>
-    <row r="9" spans="2:6">
-      <c r="B9" s="83" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="85">
+      <c r="C9" s="84">
         <v>0.72</v>
       </c>
-      <c r="D9" s="86"/>
+      <c r="D9" s="85"/>
     </row>
     <row r="10" spans="2:6" ht="16.2" thickBot="1">
-      <c r="B10" s="83" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" s="160">
+      <c r="B10" s="82" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10" s="159">
         <f>C3*C6*C7+C3*C8*C9+C3*C4*C5</f>
         <v>487.28649999999993</v>
       </c>
-      <c r="D10" s="161">
+      <c r="D10" s="160">
         <f>C10/1.13</f>
         <v>431.22699115044247</v>
       </c>
@@ -5329,6 +5492,306 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AAE205D-6326-4468-92CE-924FB684B7C9}">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="25.33203125" customWidth="1"/>
+    <col min="2" max="4" width="15.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="19.8">
+      <c r="A1" s="163" t="s">
+        <v>261</v>
+      </c>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+    </row>
+    <row r="2" spans="1:7" ht="14.4">
+      <c r="A2" s="146" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="137"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="137"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.6">
+      <c r="A4" s="164" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="164" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4" s="164" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4" s="164" t="s">
+        <v>229</v>
+      </c>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.6">
+      <c r="A5" s="165" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" s="165" t="s">
+        <v>230</v>
+      </c>
+      <c r="C5" s="165" t="s">
+        <v>231</v>
+      </c>
+      <c r="D5" s="165" t="s">
+        <v>232</v>
+      </c>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="137"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.6">
+      <c r="A6" s="165" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" s="167" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="167" t="s">
+        <v>235</v>
+      </c>
+      <c r="D6" s="167" t="s">
+        <v>236</v>
+      </c>
+      <c r="E6" s="137"/>
+      <c r="F6" s="137"/>
+      <c r="G6" s="137"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.6">
+      <c r="A7" s="165" t="s">
+        <v>237</v>
+      </c>
+      <c r="B7" s="165" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="165" t="s">
+        <v>239</v>
+      </c>
+      <c r="D7" s="165" t="s">
+        <v>240</v>
+      </c>
+      <c r="E7" s="137"/>
+      <c r="F7" s="137"/>
+      <c r="G7" s="137"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.6">
+      <c r="A8" s="165" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" s="165" t="s">
+        <v>241</v>
+      </c>
+      <c r="C8" s="165" t="s">
+        <v>242</v>
+      </c>
+      <c r="D8" s="165" t="s">
+        <v>243</v>
+      </c>
+      <c r="E8" s="137"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="137"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.6">
+      <c r="A9" s="165" t="s">
+        <v>244</v>
+      </c>
+      <c r="B9" s="167" t="s">
+        <v>245</v>
+      </c>
+      <c r="C9" s="167" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9" s="167" t="s">
+        <v>247</v>
+      </c>
+      <c r="E9" s="137"/>
+      <c r="F9" s="137"/>
+      <c r="G9" s="137"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="137"/>
+      <c r="B10" s="137"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="137"/>
+      <c r="G10" s="137"/>
+    </row>
+    <row r="11" spans="1:7" ht="19.8">
+      <c r="A11" s="163" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+    </row>
+    <row r="12" spans="1:7" ht="16.2">
+      <c r="A12" s="165" t="s">
+        <v>249</v>
+      </c>
+      <c r="B12" s="166" t="s">
+        <v>250</v>
+      </c>
+      <c r="C12" s="137"/>
+      <c r="D12" s="137"/>
+      <c r="E12" s="137"/>
+      <c r="F12" s="137"/>
+      <c r="G12" s="137"/>
+    </row>
+    <row r="13" spans="1:7" ht="16.2">
+      <c r="A13" s="165" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" s="166" t="s">
+        <v>252</v>
+      </c>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+    </row>
+    <row r="14" spans="1:7" ht="16.2">
+      <c r="A14" s="165" t="s">
+        <v>253</v>
+      </c>
+      <c r="B14" s="166" t="s">
+        <v>254</v>
+      </c>
+      <c r="C14" s="137"/>
+      <c r="D14" s="137"/>
+      <c r="E14" s="137"/>
+      <c r="F14" s="137"/>
+      <c r="G14" s="137"/>
+    </row>
+    <row r="15" spans="1:7" ht="16.2">
+      <c r="A15" s="165" t="s">
+        <v>255</v>
+      </c>
+      <c r="B15" s="166" t="s">
+        <v>256</v>
+      </c>
+      <c r="C15" s="137"/>
+      <c r="D15" s="137"/>
+      <c r="E15" s="137"/>
+      <c r="F15" s="137"/>
+      <c r="G15" s="137"/>
+    </row>
+    <row r="16" spans="1:7" ht="16.2">
+      <c r="A16" s="165" t="s">
+        <v>257</v>
+      </c>
+      <c r="B16" s="166" t="s">
+        <v>258</v>
+      </c>
+      <c r="C16" s="137"/>
+      <c r="D16" s="137"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="137"/>
+      <c r="G16" s="137"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="137"/>
+      <c r="B17" s="137"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.4">
+      <c r="A18" s="146" t="s">
+        <v>259</v>
+      </c>
+      <c r="B18" s="137"/>
+      <c r="C18" s="137"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="137"/>
+      <c r="G18" s="137"/>
+    </row>
+    <row r="19" spans="1:7" ht="14.4">
+      <c r="A19" s="146" t="s">
+        <v>260</v>
+      </c>
+      <c r="B19" s="137"/>
+      <c r="C19" s="137"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="137"/>
+      <c r="G19" s="137"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="137"/>
+      <c r="B20" s="137"/>
+      <c r="C20" s="137"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="137"/>
+      <c r="G20" s="137"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="137"/>
+      <c r="B21" s="137"/>
+      <c r="C21" s="137"/>
+      <c r="D21" s="137"/>
+      <c r="E21" s="137"/>
+      <c r="F21" s="137"/>
+      <c r="G21" s="137"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="137"/>
+      <c r="B22" s="137"/>
+      <c r="C22" s="137"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="137"/>
+      <c r="G22" s="137"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="137"/>
+      <c r="B23" s="137"/>
+      <c r="C23" s="137"/>
+      <c r="D23" s="137"/>
+      <c r="E23" s="137"/>
+      <c r="F23" s="137"/>
+      <c r="G23" s="137"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="43" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Z88"/>
   <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
@@ -5352,10 +5815,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:26" s="1" customFormat="1" ht="20.399999999999999">
-      <c r="B1" s="185" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="185"/>
+      <c r="B1" s="191" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="191"/>
     </row>
     <row r="2" spans="2:26" s="1" customFormat="1"/>
     <row r="3" spans="2:26" s="1" customFormat="1" ht="16.2">
@@ -5367,22 +5830,22 @@
         <v>600000</v>
       </c>
       <c r="E3" s="4"/>
-      <c r="F3" s="186" t="s">
+      <c r="F3" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="193"/>
+      <c r="H3" s="194" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="187"/>
-      <c r="H3" s="188" t="s">
+      <c r="I3" s="195"/>
+      <c r="J3" s="196" t="s">
         <v>67</v>
       </c>
-      <c r="I3" s="189"/>
-      <c r="J3" s="190" t="s">
-        <v>68</v>
-      </c>
-      <c r="K3" s="191"/>
-      <c r="M3" s="192" t="s">
-        <v>134</v>
-      </c>
-      <c r="N3" s="193"/>
+      <c r="K3" s="197"/>
+      <c r="M3" s="198" t="s">
+        <v>133</v>
+      </c>
+      <c r="N3" s="199"/>
     </row>
     <row r="4" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="B4" s="7" t="s">
@@ -5390,42 +5853,42 @@
       </c>
       <c r="C4" s="8">
         <f>Budget!H4</f>
-        <v>715000</v>
+        <v>500000</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="H4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>70</v>
-      </c>
       <c r="J4" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="K4" s="13" t="s">
         <v>69</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>70</v>
       </c>
       <c r="M4" s="14"/>
       <c r="N4" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="B5" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" s="8">
         <f>Budget!H5</f>
-        <v>481250</v>
+        <v>375550</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F5" s="17">
         <f>'BOM&amp;ASP'!F3</f>
@@ -5452,7 +5915,7 @@
         <v>212.47787610619471</v>
       </c>
       <c r="M5" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N5" s="22">
         <f>G22</f>
@@ -5461,14 +5924,14 @@
     </row>
     <row r="6" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="B6" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" s="8">
         <f>Budget!H6</f>
-        <v>159000</v>
+        <v>145000</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F6" s="24">
         <f>$C$16+$C$17</f>
@@ -5495,9 +5958,9 @@
         <v>0</v>
       </c>
       <c r="M6" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="N6" s="135">
+        <v>76</v>
+      </c>
+      <c r="N6" s="134">
         <f>(N5-N7)/N5</f>
         <v>0.48695479969176236</v>
       </c>
@@ -5511,15 +5974,15 @@
         <v>150000</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F7" s="24">
         <f>(C3+C4)/C20</f>
-        <v>49.810606060606062</v>
+        <v>50.925925925925924</v>
       </c>
       <c r="G7" s="18">
         <f>F7/1.13</f>
-        <v>44.080182354518641</v>
+        <v>45.067191084890204</v>
       </c>
       <c r="H7" s="24">
         <v>0</v>
@@ -5536,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N7" s="28">
         <f>G5</f>
@@ -5545,22 +6008,22 @@
     </row>
     <row r="8" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="B8" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" s="8">
         <f>Budget!H8</f>
-        <v>2032800</v>
+        <v>3003000</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F8" s="24">
         <f>(C9-C3-C4)/C20</f>
-        <v>106.93371212121212</v>
+        <v>170.07175925925927</v>
       </c>
       <c r="G8" s="18">
         <f>F8/1.13</f>
-        <v>94.631603647090387</v>
+        <v>150.5059816453622</v>
       </c>
       <c r="H8" s="24">
         <v>0</v>
@@ -5577,20 +6040,20 @@
         <v>0</v>
       </c>
       <c r="M8" s="27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N8" s="29"/>
     </row>
     <row r="9" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="B9" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" s="31">
         <f>SUM(C3:C8)</f>
-        <v>4138050</v>
+        <v>4773550</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F9" s="32">
         <v>0</v>
@@ -5616,16 +6079,16 @@
         <v>0</v>
       </c>
       <c r="M9" s="27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N9" s="33">
         <f>SUM(C20:C26)</f>
-        <v>79200</v>
+        <v>64800</v>
       </c>
     </row>
     <row r="10" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="E10" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F10" s="34">
         <v>0.57999999999999996</v>
@@ -5651,22 +6114,22 @@
         <v>0.53211009174311896</v>
       </c>
       <c r="M10" s="27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N10" s="35">
         <f>G28+I28+K28</f>
-        <v>33338668.185345128</v>
+        <v>27277092.151646018</v>
       </c>
     </row>
     <row r="11" spans="2:26" ht="15.6">
       <c r="B11" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="36">
+        <v>0</v>
+      </c>
+      <c r="E11" s="23" t="s">
         <v>88</v>
-      </c>
-      <c r="C11" s="36">
-        <v>0</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>89</v>
       </c>
       <c r="F11" s="24">
         <f t="shared" ref="F11:K11" si="0">F10+F9</f>
@@ -5693,23 +6156,23 @@
         <v>0.53211009174311896</v>
       </c>
       <c r="M11" s="27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N11" s="35">
         <f>G23*G27+I23*I27+K23*K27</f>
-        <v>16164650.486230083</v>
+        <v>13225623.125097342</v>
       </c>
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="2:26" ht="15.6">
       <c r="B12" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="40">
+        <v>0</v>
+      </c>
+      <c r="E12" s="16" t="s">
         <v>91</v>
-      </c>
-      <c r="C12" s="40">
-        <v>0</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>92</v>
       </c>
       <c r="F12" s="41">
         <v>0.05</v>
@@ -5733,7 +6196,7 @@
         <v>0.05</v>
       </c>
       <c r="M12" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N12" s="45">
         <f>N11/N10</f>
@@ -5742,13 +6205,13 @@
     </row>
     <row r="13" spans="2:26" s="2" customFormat="1" ht="15.6">
       <c r="B13" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="40">
+        <v>0</v>
+      </c>
+      <c r="E13" s="23" t="s">
         <v>94</v>
-      </c>
-      <c r="C13" s="40">
-        <v>0</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>95</v>
       </c>
       <c r="F13" s="24">
         <f>F12*F5</f>
@@ -5775,22 +6238,22 @@
         <v>12.005000000000001</v>
       </c>
       <c r="M13" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N13" s="35">
         <f>G29+I29+K29</f>
-        <v>-206533.60450513591</v>
+        <v>-1397187.9933883543</v>
       </c>
     </row>
     <row r="14" spans="2:26" s="3" customFormat="1" ht="15.6">
       <c r="B14" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="40">
+        <v>0</v>
+      </c>
+      <c r="E14" s="16" t="s">
         <v>97</v>
-      </c>
-      <c r="C14" s="40">
-        <v>0</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>98</v>
       </c>
       <c r="F14" s="41">
         <v>1.7000000000000001E-2</v>
@@ -5816,22 +6279,22 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="M14" s="26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N14" s="46">
         <f>N13/N10</f>
-        <v>-6.1950166502428876E-3</v>
+        <v>-5.1222028565975346E-2</v>
       </c>
     </row>
     <row r="15" spans="2:26" s="3" customFormat="1" ht="15.6">
       <c r="B15" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="40">
+        <v>0</v>
+      </c>
+      <c r="E15" s="23" t="s">
         <v>100</v>
-      </c>
-      <c r="C15" s="40">
-        <v>0</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>101</v>
       </c>
       <c r="F15" s="24">
         <f>C28*F14</f>
@@ -5858,23 +6321,23 @@
         <v>3.7610619469026552</v>
       </c>
       <c r="M15" s="21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N15" s="47">
         <f>C9</f>
-        <v>4138050</v>
+        <v>4773550</v>
       </c>
     </row>
     <row r="16" spans="2:26" s="3" customFormat="1" ht="15.6">
       <c r="B16" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C16" s="48">
         <f>SUM(C11:C15)</f>
         <v>0</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F16" s="24">
         <f t="shared" ref="F16:K16" si="1">F15</f>
@@ -5901,22 +6364,22 @@
         <v>3.7610619469026552</v>
       </c>
       <c r="M16" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="N16" s="49">
+        <v>104</v>
+      </c>
+      <c r="N16" s="162">
         <f>N13/N15</f>
-        <v>-4.9910852818389313E-2</v>
+        <v>-0.2926936961775522</v>
       </c>
     </row>
     <row r="17" spans="2:14" s="3" customFormat="1" ht="15.6">
       <c r="B17" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="49">
+        <v>0</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>106</v>
-      </c>
-      <c r="C17" s="50">
-        <v>0</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>107</v>
       </c>
       <c r="F17" s="41">
         <v>5.0000000000000001E-3</v>
@@ -5939,7 +6402,7 @@
     </row>
     <row r="18" spans="2:14">
       <c r="E18" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F18" s="24">
         <f>F5*F17</f>
@@ -5967,11 +6430,11 @@
       </c>
     </row>
     <row r="19" spans="2:14" ht="15.6">
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>109</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>110</v>
       </c>
       <c r="F19" s="41">
         <v>0.3</v>
@@ -5994,15 +6457,15 @@
     </row>
     <row r="20" spans="2:14">
       <c r="B20" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="52">
+        <v>110</v>
+      </c>
+      <c r="C20" s="51">
         <f>Scenarios!C4</f>
-        <v>26400</v>
+        <v>21600</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F20" s="24">
         <f>F19*F22</f>
@@ -6028,29 +6491,29 @@
         <f>J20</f>
         <v>139.53262637999995</v>
       </c>
-      <c r="M20" s="156">
+      <c r="M20" s="155">
         <f>F20*C20+H20*C21+J20*C22</f>
-        <v>11301808.514831997</v>
+        <v>9246934.2394079976</v>
       </c>
     </row>
     <row r="21" spans="2:14" s="3" customFormat="1" ht="15.6">
       <c r="B21" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="52">
+        <f>Scenarios!C5</f>
+        <v>21600</v>
+      </c>
+      <c r="E21" s="53" t="s">
         <v>113</v>
-      </c>
-      <c r="C21" s="53">
-        <f>Scenarios!C5</f>
-        <v>26400</v>
-      </c>
-      <c r="E21" s="54" t="s">
-        <v>114</v>
       </c>
       <c r="F21" s="24">
         <f t="shared" ref="F21:K21" si="2">F5+F6++F7+F8+F11+F13+F16+F18+F20</f>
-        <v>571.51026818181811</v>
+        <v>635.76363518518519</v>
       </c>
       <c r="G21" s="18">
         <f t="shared" si="2"/>
-        <v>524.17984609335213</v>
+        <v>581.04123282199555</v>
       </c>
       <c r="H21" s="37">
         <f t="shared" si="2"/>
@@ -6071,20 +6534,20 @@
     </row>
     <row r="22" spans="2:14" ht="15.6">
       <c r="B22" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22" s="53">
+        <v>114</v>
+      </c>
+      <c r="C22" s="52">
         <f>Scenarios!C6</f>
-        <v>26400</v>
+        <v>21600</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F22" s="17">
         <f>'BOM&amp;ASP'!C10</f>
         <v>487.28649999999993</v>
       </c>
-      <c r="G22" s="55">
+      <c r="G22" s="54">
         <f>F22/1.13</f>
         <v>431.22699115044247</v>
       </c>
@@ -6092,7 +6555,7 @@
         <f>(F22-3)*0.98</f>
         <v>474.6007699999999</v>
       </c>
-      <c r="I22" s="56">
+      <c r="I22" s="55">
         <f>H22/1.13</f>
         <v>420.00068141592914</v>
       </c>
@@ -6100,16 +6563,16 @@
         <f>H22*0.98</f>
         <v>465.10875459999988</v>
       </c>
-      <c r="K22" s="57">
+      <c r="K22" s="56">
         <f>J22/1.13</f>
         <v>411.60066778761058</v>
       </c>
     </row>
     <row r="23" spans="2:14">
       <c r="B23" s="7"/>
-      <c r="C23" s="58"/>
+      <c r="C23" s="57"/>
       <c r="E23" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F23" s="24">
         <f t="shared" ref="F23:K23" si="3">F22-F5</f>
@@ -6138,15 +6601,15 @@
     </row>
     <row r="24" spans="2:14" ht="15.6">
       <c r="B24" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="58">
+        <v>0</v>
+      </c>
+      <c r="E24" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="C24" s="59">
-        <v>0</v>
-      </c>
-      <c r="E24" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="F24" s="60">
+      <c r="F24" s="59">
         <f t="shared" ref="F24:K24" si="4">F23/F22</f>
         <v>0.48695479969176236</v>
       </c>
@@ -6154,7 +6617,7 @@
         <f t="shared" si="4"/>
         <v>0.48695479969176236</v>
       </c>
-      <c r="H24" s="60">
+      <c r="H24" s="59">
         <f t="shared" si="4"/>
         <v>0.4837766487399503</v>
       </c>
@@ -6162,7 +6625,7 @@
         <f t="shared" si="4"/>
         <v>0.4837766487399503</v>
       </c>
-      <c r="J24" s="60">
+      <c r="J24" s="59">
         <f t="shared" si="4"/>
         <v>0.4837766487399503</v>
       </c>
@@ -6173,21 +6636,21 @@
     </row>
     <row r="25" spans="2:14">
       <c r="B25" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="58">
+        <v>0</v>
+      </c>
+      <c r="E25" s="23" t="s">
         <v>119</v>
-      </c>
-      <c r="C25" s="59">
-        <v>0</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>120</v>
       </c>
       <c r="F25" s="24">
         <f t="shared" ref="F25:K25" si="5">F22-F21</f>
-        <v>-84.223768181818173</v>
+        <v>-148.47713518518526</v>
       </c>
       <c r="G25" s="18">
         <f t="shared" si="5"/>
-        <v>-92.952854942909653</v>
+        <v>-149.81424167155308</v>
       </c>
       <c r="H25" s="24">
         <f t="shared" si="5"/>
@@ -6208,23 +6671,23 @@
     </row>
     <row r="26" spans="2:14" ht="15.6">
       <c r="B26" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="60">
+        <v>0</v>
+      </c>
+      <c r="E26" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="C26" s="61">
-        <v>0</v>
-      </c>
-      <c r="E26" s="54" t="s">
-        <v>122</v>
-      </c>
-      <c r="F26" s="60">
+      <c r="F26" s="59">
         <f t="shared" ref="F26:K26" si="6">F25/F22</f>
-        <v>-0.17284240007022189</v>
+        <v>-0.30470192624910658</v>
       </c>
       <c r="G26" s="42">
         <f t="shared" si="6"/>
-        <v>-0.21555435269700249</v>
-      </c>
-      <c r="H26" s="60">
+        <v>-0.34741387887588715</v>
+      </c>
+      <c r="H26" s="59">
         <f t="shared" si="6"/>
         <v>0.14520738978152073</v>
       </c>
@@ -6232,7 +6695,7 @@
         <f t="shared" si="6"/>
         <v>0.10247154585596281</v>
       </c>
-      <c r="J26" s="60">
+      <c r="J26" s="59">
         <f t="shared" si="6"/>
         <v>0.14499969642153876</v>
       </c>
@@ -6244,115 +6707,115 @@
       <c r="N26" s="3"/>
     </row>
     <row r="27" spans="2:14" ht="15.6">
-      <c r="E27" s="54" t="s">
-        <v>123</v>
-      </c>
-      <c r="F27" s="62">
+      <c r="E27" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" s="61">
         <f>C20+C24</f>
-        <v>26400</v>
-      </c>
-      <c r="G27" s="63">
+        <v>21600</v>
+      </c>
+      <c r="G27" s="62">
         <f>F27</f>
-        <v>26400</v>
-      </c>
-      <c r="H27" s="64">
+        <v>21600</v>
+      </c>
+      <c r="H27" s="63">
         <f>C21+C25</f>
-        <v>26400</v>
-      </c>
-      <c r="I27" s="65">
+        <v>21600</v>
+      </c>
+      <c r="I27" s="64">
         <f>H27</f>
-        <v>26400</v>
-      </c>
-      <c r="J27" s="64">
+        <v>21600</v>
+      </c>
+      <c r="J27" s="63">
         <f>C22+C26</f>
-        <v>26400</v>
-      </c>
-      <c r="K27" s="66">
+        <v>21600</v>
+      </c>
+      <c r="K27" s="65">
         <f>J27</f>
-        <v>26400</v>
-      </c>
-      <c r="M27" s="67"/>
-      <c r="N27" s="67"/>
+        <v>21600</v>
+      </c>
+      <c r="M27" s="66"/>
+      <c r="N27" s="66"/>
     </row>
     <row r="28" spans="2:14" ht="15.6">
       <c r="B28" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C28" s="36">
         <f>F5</f>
         <v>250</v>
       </c>
-      <c r="E28" s="54" t="s">
-        <v>125</v>
-      </c>
-      <c r="F28" s="68">
+      <c r="E28" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" s="67">
         <f t="shared" ref="F28:K28" si="7">F27*F22</f>
-        <v>12864363.599999998</v>
+        <v>10525388.399999999</v>
       </c>
       <c r="G28" s="18">
         <f t="shared" si="7"/>
-        <v>11384392.566371681</v>
-      </c>
-      <c r="H28" s="69">
+        <v>9314503.0088495575</v>
+      </c>
+      <c r="H28" s="68">
         <f t="shared" si="7"/>
-        <v>12529460.327999998</v>
-      </c>
-      <c r="I28" s="70">
+        <v>10251376.631999997</v>
+      </c>
+      <c r="I28" s="69">
         <f t="shared" si="7"/>
-        <v>11088017.989380529</v>
-      </c>
-      <c r="J28" s="69">
+        <v>9072014.71858407</v>
+      </c>
+      <c r="J28" s="68">
         <f t="shared" si="7"/>
-        <v>12278871.121439997</v>
-      </c>
-      <c r="K28" s="71">
+        <v>10046349.099359997</v>
+      </c>
+      <c r="K28" s="70">
         <f t="shared" si="7"/>
-        <v>10866257.62959292</v>
+        <v>8890574.4242123887</v>
       </c>
     </row>
     <row r="29" spans="2:14" ht="15.6">
       <c r="B29" s="30"/>
-      <c r="C29" s="50"/>
-      <c r="E29" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="F29" s="72">
+      <c r="C29" s="49"/>
+      <c r="E29" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="F29" s="71">
         <f t="shared" ref="F29:K29" si="8">F27*F25</f>
-        <v>-2223507.48</v>
-      </c>
-      <c r="G29" s="73">
+        <v>-3207106.1200000015</v>
+      </c>
+      <c r="G29" s="72">
         <f t="shared" si="8"/>
-        <v>-2453955.370492815</v>
-      </c>
-      <c r="H29" s="74">
+        <v>-3235987.6201055464</v>
+      </c>
+      <c r="H29" s="73">
         <f t="shared" si="8"/>
-        <v>1819370.2295999962</v>
-      </c>
-      <c r="I29" s="75">
+        <v>1488575.6423999968</v>
+      </c>
+      <c r="I29" s="74">
         <f t="shared" si="8"/>
-        <v>1136206.3438505474</v>
-      </c>
-      <c r="J29" s="74">
+        <v>929623.37224135711</v>
+      </c>
+      <c r="J29" s="73">
         <f t="shared" si="8"/>
-        <v>1780432.5850079986</v>
-      </c>
-      <c r="K29" s="76">
+        <v>1456717.569551999</v>
+      </c>
+      <c r="K29" s="75">
         <f t="shared" si="8"/>
-        <v>1111215.4221371317</v>
+        <v>909176.25447583513</v>
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="77"/>
-      <c r="D39" s="78"/>
+      <c r="A39" s="76"/>
+      <c r="D39" s="77"/>
     </row>
     <row r="40" spans="1:10">
       <c r="D40" s="1"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="D43" s="79"/>
+      <c r="D43" s="78"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="J46" s="51"/>
+      <c r="J46" s="50"/>
     </row>
     <row r="50" spans="8:11">
       <c r="J50" s="1"/>
@@ -6372,7 +6835,7 @@
     </row>
     <row r="54" spans="8:11">
       <c r="J54" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K54" s="1"/>
     </row>
@@ -6469,7 +6932,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Z88"/>
   <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
@@ -6493,10 +6956,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:26" s="1" customFormat="1" ht="20.399999999999999">
-      <c r="B1" s="185" t="s">
-        <v>128</v>
-      </c>
-      <c r="C1" s="185"/>
+      <c r="B1" s="191" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="191"/>
     </row>
     <row r="2" spans="2:26" s="1" customFormat="1"/>
     <row r="3" spans="2:26" s="1" customFormat="1" ht="16.2">
@@ -6508,22 +6971,22 @@
         <v>600000</v>
       </c>
       <c r="E3" s="4"/>
-      <c r="F3" s="186" t="s">
+      <c r="F3" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="193"/>
+      <c r="H3" s="194" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="187"/>
-      <c r="H3" s="188" t="s">
+      <c r="I3" s="195"/>
+      <c r="J3" s="196" t="s">
         <v>67</v>
       </c>
-      <c r="I3" s="189"/>
-      <c r="J3" s="190" t="s">
-        <v>68</v>
-      </c>
-      <c r="K3" s="191"/>
-      <c r="M3" s="192" t="s">
-        <v>132</v>
-      </c>
-      <c r="N3" s="193"/>
+      <c r="K3" s="197"/>
+      <c r="M3" s="198" t="s">
+        <v>131</v>
+      </c>
+      <c r="N3" s="199"/>
     </row>
     <row r="4" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="B4" s="7" t="s">
@@ -6531,42 +6994,42 @@
       </c>
       <c r="C4" s="8">
         <f>Budget!H4</f>
-        <v>715000</v>
+        <v>500000</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="H4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>70</v>
-      </c>
       <c r="J4" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="K4" s="13" t="s">
         <v>69</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>70</v>
       </c>
       <c r="M4" s="14"/>
       <c r="N4" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="B5" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" s="8">
         <f>Budget!H5</f>
-        <v>481250</v>
+        <v>375550</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F5" s="17">
         <f>'BOM&amp;ASP'!F3</f>
@@ -6593,7 +7056,7 @@
         <v>212.47787610619471</v>
       </c>
       <c r="M5" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N5" s="22">
         <f>G22</f>
@@ -6602,14 +7065,14 @@
     </row>
     <row r="6" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="B6" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" s="8">
         <f>Budget!H6</f>
-        <v>159000</v>
+        <v>145000</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F6" s="24">
         <f t="shared" ref="F6:J6" si="1">$C$16+$C$17</f>
@@ -6636,9 +7099,9 @@
         <v>0</v>
       </c>
       <c r="M6" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="N6" s="135">
+        <v>76</v>
+      </c>
+      <c r="N6" s="134">
         <f>(N5-N7)/N5</f>
         <v>0.48695479969176236</v>
       </c>
@@ -6652,15 +7115,15 @@
         <v>150000</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F7" s="24">
         <f>(C3+C4-D3)/C20</f>
-        <v>35.3494623655914</v>
+        <v>33.950617283950621</v>
       </c>
       <c r="G7" s="18">
         <f t="shared" ref="G7:K7" si="3">F7/1.13</f>
-        <v>31.282710058045488</v>
+        <v>30.044794056593471</v>
       </c>
       <c r="H7" s="24">
         <v>0</v>
@@ -6677,7 +7140,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N7" s="28">
         <f>G5</f>
@@ -6686,22 +7149,22 @@
     </row>
     <row r="8" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="B8" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" s="8">
         <f>Budget!H8</f>
-        <v>2032800</v>
+        <v>3003000</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F8" s="24">
         <f>(C9-C3-C4)/C20</f>
-        <v>75.888440860215056</v>
+        <v>113.38117283950618</v>
       </c>
       <c r="G8" s="18">
         <f>F8/1.13</f>
-        <v>67.157912265677041</v>
+        <v>100.33732109690813</v>
       </c>
       <c r="H8" s="24">
         <v>0</v>
@@ -6718,20 +7181,20 @@
         <v>0</v>
       </c>
       <c r="M8" s="27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N8" s="29"/>
     </row>
     <row r="9" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="B9" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" s="31">
         <f>SUM(C3:C8)</f>
-        <v>4138050</v>
+        <v>4773550</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F9" s="32">
         <v>0</v>
@@ -6757,16 +7220,16 @@
         <v>0</v>
       </c>
       <c r="M9" s="27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N9" s="33">
         <f>SUM(C20:C26)</f>
-        <v>111600</v>
+        <v>97200</v>
       </c>
     </row>
     <row r="10" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="E10" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F10" s="34">
         <v>0.57999999999999996</v>
@@ -6792,22 +7255,22 @@
         <v>0.53211009174311896</v>
       </c>
       <c r="M10" s="27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N10" s="35">
         <f>G28+I28+K28</f>
-        <v>46977214.261168137</v>
+        <v>40915638.227469027</v>
       </c>
     </row>
     <row r="11" spans="2:26" ht="15.6">
       <c r="B11" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="36">
+        <v>0</v>
+      </c>
+      <c r="E11" s="23" t="s">
         <v>88</v>
-      </c>
-      <c r="C11" s="36">
-        <v>0</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>89</v>
       </c>
       <c r="F11" s="24">
         <f t="shared" ref="F11:K11" si="7">F10+F9</f>
@@ -6834,23 +7297,23 @@
         <v>0.53211009174311896</v>
       </c>
       <c r="M11" s="27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N11" s="35">
         <f>G23*G27+I23*I27+K23*K27</f>
-        <v>22777462.048778754</v>
+        <v>19838434.687646009</v>
       </c>
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="2:26" ht="15.6">
       <c r="B12" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="40">
+        <v>0</v>
+      </c>
+      <c r="E12" s="16" t="s">
         <v>91</v>
-      </c>
-      <c r="C12" s="40">
-        <v>0</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>92</v>
       </c>
       <c r="F12" s="41">
         <v>0.05</v>
@@ -6874,22 +7337,22 @@
         <v>0.05</v>
       </c>
       <c r="M12" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N12" s="45">
         <f>N11/N10</f>
-        <v>0.48486191459008765</v>
+        <v>0.48486191459008754</v>
       </c>
     </row>
     <row r="13" spans="2:26" s="2" customFormat="1" ht="15.6">
       <c r="B13" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="40">
+        <v>0</v>
+      </c>
+      <c r="E13" s="23" t="s">
         <v>94</v>
-      </c>
-      <c r="C13" s="40">
-        <v>0</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>95</v>
       </c>
       <c r="F13" s="24">
         <f t="shared" ref="F13:J13" si="9">F12*F5</f>
@@ -6916,22 +7379,22 @@
         <v>12.005000000000001</v>
       </c>
       <c r="M13" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N13" s="35">
         <f>G29+I29+K29</f>
-        <v>1207062.6642874153</v>
+        <v>16408.275404195767</v>
       </c>
     </row>
     <row r="14" spans="2:26" s="3" customFormat="1" ht="15.6">
       <c r="B14" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="40">
+        <v>0</v>
+      </c>
+      <c r="E14" s="16" t="s">
         <v>97</v>
-      </c>
-      <c r="C14" s="40">
-        <v>0</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>98</v>
       </c>
       <c r="F14" s="41">
         <v>1.7000000000000001E-2</v>
@@ -6957,22 +7420,22 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="M14" s="26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N14" s="46">
         <f>N13/N10</f>
-        <v>2.5694641184485605E-2</v>
+        <v>4.0102699395704272E-4</v>
       </c>
     </row>
     <row r="15" spans="2:26" s="3" customFormat="1" ht="15.6">
       <c r="B15" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="40">
+        <v>0</v>
+      </c>
+      <c r="E15" s="23" t="s">
         <v>100</v>
-      </c>
-      <c r="C15" s="40">
-        <v>0</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>101</v>
       </c>
       <c r="F15" s="24">
         <f>C28*F14</f>
@@ -6999,23 +7462,23 @@
         <v>3.7610619469026552</v>
       </c>
       <c r="M15" s="21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N15" s="47">
         <f>C9</f>
-        <v>4138050</v>
+        <v>4773550</v>
       </c>
     </row>
     <row r="16" spans="2:26" s="3" customFormat="1" ht="15.6">
       <c r="B16" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C16" s="48">
         <f>SUM(C11:C15)</f>
         <v>0</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F16" s="24">
         <f t="shared" ref="F16:K16" si="13">F15</f>
@@ -7042,22 +7505,22 @@
         <v>3.7610619469026552</v>
       </c>
       <c r="M16" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="N16" s="49">
+        <v>104</v>
+      </c>
+      <c r="N16" s="162">
         <f>N13/N15</f>
-        <v>0.29169842420642944</v>
+        <v>3.437331839866717E-3</v>
       </c>
     </row>
     <row r="17" spans="2:14" s="3" customFormat="1" ht="15.6">
       <c r="B17" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="49">
+        <v>0</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>106</v>
-      </c>
-      <c r="C17" s="50">
-        <v>0</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>107</v>
       </c>
       <c r="F17" s="41">
         <v>5.0000000000000001E-3</v>
@@ -7080,7 +7543,7 @@
     </row>
     <row r="18" spans="2:14">
       <c r="E18" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F18" s="24">
         <f t="shared" ref="F18:J18" si="14">F5*F17</f>
@@ -7108,11 +7571,11 @@
       </c>
     </row>
     <row r="19" spans="2:14" ht="15.6">
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>109</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>110</v>
       </c>
       <c r="F19" s="41">
         <v>0.3</v>
@@ -7135,15 +7598,15 @@
     </row>
     <row r="20" spans="2:14">
       <c r="B20" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="52">
+        <v>110</v>
+      </c>
+      <c r="C20" s="51">
         <f>Scenarios!C12</f>
-        <v>37200</v>
+        <v>32400</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F20" s="24">
         <f t="shared" ref="F20:J20" si="16">F19*F22</f>
@@ -7169,29 +7632,29 @@
         <f t="shared" si="17"/>
         <v>139.53262637999995</v>
       </c>
-      <c r="M20" s="156">
+      <c r="M20" s="155">
         <f>F20*C20+H20*C21+J20*C22</f>
-        <v>15925275.634535996</v>
+        <v>13870401.359111996</v>
       </c>
     </row>
     <row r="21" spans="2:14" s="3" customFormat="1" ht="15.6">
       <c r="B21" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="52">
+        <f>Scenarios!C13</f>
+        <v>32400</v>
+      </c>
+      <c r="E21" s="53" t="s">
         <v>113</v>
-      </c>
-      <c r="C21" s="53">
-        <f>Scenarios!C13</f>
-        <v>37200</v>
-      </c>
-      <c r="E21" s="54" t="s">
-        <v>114</v>
       </c>
       <c r="F21" s="24">
         <f t="shared" ref="F21:K21" si="18">F5+F6++F7+F8+F11+F13+F16+F18+F20</f>
-        <v>526.00385322580644</v>
+        <v>562.09774012345679</v>
       </c>
       <c r="G21" s="18">
         <f t="shared" si="18"/>
-        <v>483.90868241546559</v>
+        <v>515.85017524524471</v>
       </c>
       <c r="H21" s="37">
         <f t="shared" si="18"/>
@@ -7212,20 +7675,20 @@
     </row>
     <row r="22" spans="2:14" ht="15.6">
       <c r="B22" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22" s="53">
+        <v>114</v>
+      </c>
+      <c r="C22" s="52">
         <f>Scenarios!C14</f>
-        <v>37200</v>
+        <v>32400</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F22" s="17">
         <f>'BOM&amp;ASP'!C10</f>
         <v>487.28649999999993</v>
       </c>
-      <c r="G22" s="55">
+      <c r="G22" s="54">
         <f t="shared" ref="G22:K22" si="19">F22/1.13</f>
         <v>431.22699115044247</v>
       </c>
@@ -7233,7 +7696,7 @@
         <f>(F22-3)*0.98</f>
         <v>474.6007699999999</v>
       </c>
-      <c r="I22" s="56">
+      <c r="I22" s="55">
         <f t="shared" si="19"/>
         <v>420.00068141592914</v>
       </c>
@@ -7241,16 +7704,16 @@
         <f>H22*0.98</f>
         <v>465.10875459999988</v>
       </c>
-      <c r="K22" s="57">
+      <c r="K22" s="56">
         <f t="shared" si="19"/>
         <v>411.60066778761058</v>
       </c>
     </row>
     <row r="23" spans="2:14">
       <c r="B23" s="7"/>
-      <c r="C23" s="58"/>
+      <c r="C23" s="57"/>
       <c r="E23" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F23" s="24">
         <f t="shared" ref="F23:K23" si="20">F22-F5</f>
@@ -7279,15 +7742,15 @@
     </row>
     <row r="24" spans="2:14" ht="15.6">
       <c r="B24" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="58">
+        <v>0</v>
+      </c>
+      <c r="E24" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="C24" s="59">
-        <v>0</v>
-      </c>
-      <c r="E24" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="F24" s="60">
+      <c r="F24" s="59">
         <f t="shared" ref="F24:K24" si="21">F23/F22</f>
         <v>0.48695479969176236</v>
       </c>
@@ -7295,7 +7758,7 @@
         <f t="shared" si="21"/>
         <v>0.48695479969176236</v>
       </c>
-      <c r="H24" s="60">
+      <c r="H24" s="59">
         <f t="shared" si="21"/>
         <v>0.4837766487399503</v>
       </c>
@@ -7303,7 +7766,7 @@
         <f t="shared" si="21"/>
         <v>0.4837766487399503</v>
       </c>
-      <c r="J24" s="60">
+      <c r="J24" s="59">
         <f t="shared" si="21"/>
         <v>0.4837766487399503</v>
       </c>
@@ -7314,21 +7777,21 @@
     </row>
     <row r="25" spans="2:14">
       <c r="B25" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="58">
+        <v>0</v>
+      </c>
+      <c r="E25" s="23" t="s">
         <v>119</v>
-      </c>
-      <c r="C25" s="59">
-        <v>0</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>120</v>
       </c>
       <c r="F25" s="24">
         <f t="shared" ref="F25:K25" si="22">F22-F21</f>
-        <v>-38.717353225806505</v>
+        <v>-74.811240123456855</v>
       </c>
       <c r="G25" s="18">
         <f t="shared" si="22"/>
-        <v>-52.681691265023119</v>
+        <v>-84.623184094802241</v>
       </c>
       <c r="H25" s="24">
         <f t="shared" si="22"/>
@@ -7349,23 +7812,23 @@
     </row>
     <row r="26" spans="2:14" ht="15.6">
       <c r="B26" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="60">
+        <v>0</v>
+      </c>
+      <c r="E26" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="C26" s="61">
-        <v>0</v>
-      </c>
-      <c r="E26" s="54" t="s">
-        <v>122</v>
-      </c>
-      <c r="F26" s="60">
+      <c r="F26" s="59">
         <f t="shared" ref="F26:K26" si="23">F25/F22</f>
-        <v>-7.9455008964554749E-2</v>
+        <v>-0.15352619069778634</v>
       </c>
       <c r="G26" s="42">
         <f t="shared" si="23"/>
-        <v>-0.12216696159133512</v>
-      </c>
-      <c r="H26" s="60">
+        <v>-0.19623814332456682</v>
+      </c>
+      <c r="H26" s="59">
         <f t="shared" si="23"/>
         <v>0.14520738978152073</v>
       </c>
@@ -7373,7 +7836,7 @@
         <f t="shared" si="23"/>
         <v>0.10247154585596281</v>
       </c>
-      <c r="J26" s="60">
+      <c r="J26" s="59">
         <f t="shared" si="23"/>
         <v>0.14499969642153876</v>
       </c>
@@ -7385,115 +7848,115 @@
       <c r="N26" s="3"/>
     </row>
     <row r="27" spans="2:14" ht="15.6">
-      <c r="E27" s="54" t="s">
-        <v>123</v>
-      </c>
-      <c r="F27" s="62">
+      <c r="E27" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" s="61">
         <f>C20+C24</f>
-        <v>37200</v>
-      </c>
-      <c r="G27" s="63">
+        <v>32400</v>
+      </c>
+      <c r="G27" s="62">
         <f t="shared" ref="G27:K27" si="24">F27</f>
-        <v>37200</v>
-      </c>
-      <c r="H27" s="64">
+        <v>32400</v>
+      </c>
+      <c r="H27" s="63">
         <f>C21+C25</f>
-        <v>37200</v>
-      </c>
-      <c r="I27" s="65">
+        <v>32400</v>
+      </c>
+      <c r="I27" s="64">
         <f t="shared" si="24"/>
-        <v>37200</v>
-      </c>
-      <c r="J27" s="64">
+        <v>32400</v>
+      </c>
+      <c r="J27" s="63">
         <f>C22+C26</f>
-        <v>37200</v>
-      </c>
-      <c r="K27" s="66">
+        <v>32400</v>
+      </c>
+      <c r="K27" s="65">
         <f t="shared" si="24"/>
-        <v>37200</v>
-      </c>
-      <c r="M27" s="67"/>
-      <c r="N27" s="67"/>
+        <v>32400</v>
+      </c>
+      <c r="M27" s="66"/>
+      <c r="N27" s="66"/>
     </row>
     <row r="28" spans="2:14" ht="15.6">
       <c r="B28" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C28" s="36">
         <f>F5</f>
         <v>250</v>
       </c>
-      <c r="E28" s="54" t="s">
-        <v>125</v>
-      </c>
-      <c r="F28" s="68">
+      <c r="E28" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" s="67">
         <f t="shared" ref="F28:K28" si="25">F27*F22</f>
-        <v>18127057.799999997</v>
+        <v>15788082.599999998</v>
       </c>
       <c r="G28" s="18">
         <f t="shared" si="25"/>
-        <v>16041644.07079646</v>
-      </c>
-      <c r="H28" s="69">
+        <v>13971754.513274336</v>
+      </c>
+      <c r="H28" s="68">
         <f t="shared" si="25"/>
-        <v>17655148.643999998</v>
-      </c>
-      <c r="I28" s="70">
+        <v>15377064.947999997</v>
+      </c>
+      <c r="I28" s="69">
         <f t="shared" si="25"/>
-        <v>15624025.348672563</v>
-      </c>
-      <c r="J28" s="69">
+        <v>13608022.077876104</v>
+      </c>
+      <c r="J28" s="68">
         <f t="shared" si="25"/>
-        <v>17302045.671119995</v>
-      </c>
-      <c r="K28" s="71">
+        <v>15069523.649039997</v>
+      </c>
+      <c r="K28" s="70">
         <f t="shared" si="25"/>
-        <v>15311544.841699114</v>
+        <v>13335861.636318583</v>
       </c>
     </row>
     <row r="29" spans="2:14" ht="15.6">
       <c r="B29" s="30"/>
-      <c r="C29" s="50"/>
-      <c r="E29" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="F29" s="72">
+      <c r="C29" s="49"/>
+      <c r="E29" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="F29" s="71">
         <f t="shared" ref="F29:K29" si="26">F27*F25</f>
-        <v>-1440285.5400000019</v>
-      </c>
-      <c r="G29" s="73">
+        <v>-2423884.180000002</v>
+      </c>
+      <c r="G29" s="72">
         <f t="shared" si="26"/>
-        <v>-1959758.9150588601</v>
-      </c>
-      <c r="H29" s="74">
+        <v>-2741791.1646715924</v>
+      </c>
+      <c r="H29" s="73">
         <f t="shared" si="26"/>
-        <v>2563658.0507999947</v>
-      </c>
-      <c r="I29" s="75">
+        <v>2232863.4635999952</v>
+      </c>
+      <c r="I29" s="74">
         <f t="shared" si="26"/>
-        <v>1601018.0299712261</v>
-      </c>
-      <c r="J29" s="74">
+        <v>1394435.0583620355</v>
+      </c>
+      <c r="J29" s="73">
         <f t="shared" si="26"/>
-        <v>2508791.369783998</v>
-      </c>
-      <c r="K29" s="76">
+        <v>2185076.3543279986</v>
+      </c>
+      <c r="K29" s="75">
         <f t="shared" si="26"/>
-        <v>1565803.5493750493</v>
+        <v>1363764.3817137526</v>
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="77"/>
-      <c r="D39" s="78"/>
+      <c r="A39" s="76"/>
+      <c r="D39" s="77"/>
     </row>
     <row r="40" spans="1:10">
       <c r="D40" s="1"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="D43" s="79"/>
+      <c r="D43" s="78"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="J46" s="51"/>
+      <c r="J46" s="50"/>
     </row>
     <row r="50" spans="8:11">
       <c r="J50" s="1"/>
@@ -7513,7 +7976,7 @@
     </row>
     <row r="54" spans="8:11">
       <c r="J54" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K54" s="1"/>
     </row>
@@ -7610,7 +8073,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:Z88"/>
   <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
@@ -7634,10 +8097,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:26" s="1" customFormat="1" ht="20.399999999999999">
-      <c r="B1" s="194" t="s">
-        <v>129</v>
-      </c>
-      <c r="C1" s="194"/>
+      <c r="B1" s="200" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" s="200"/>
     </row>
     <row r="2" spans="2:26" s="1" customFormat="1"/>
     <row r="3" spans="2:26" s="1" customFormat="1" ht="16.2">
@@ -7649,22 +8112,22 @@
         <v>600000</v>
       </c>
       <c r="E3" s="4"/>
-      <c r="F3" s="186" t="s">
+      <c r="F3" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="193"/>
+      <c r="H3" s="194" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="187"/>
-      <c r="H3" s="188" t="s">
+      <c r="I3" s="195"/>
+      <c r="J3" s="196" t="s">
         <v>67</v>
       </c>
-      <c r="I3" s="189"/>
-      <c r="J3" s="190" t="s">
-        <v>68</v>
-      </c>
-      <c r="K3" s="191"/>
-      <c r="M3" s="192" t="s">
-        <v>133</v>
-      </c>
-      <c r="N3" s="193"/>
+      <c r="K3" s="197"/>
+      <c r="M3" s="198" t="s">
+        <v>132</v>
+      </c>
+      <c r="N3" s="199"/>
     </row>
     <row r="4" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="B4" s="7" t="s">
@@ -7672,42 +8135,42 @@
       </c>
       <c r="C4" s="8">
         <f>Budget!H4</f>
-        <v>715000</v>
+        <v>500000</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="H4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>70</v>
-      </c>
       <c r="J4" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="K4" s="13" t="s">
         <v>69</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>70</v>
       </c>
       <c r="M4" s="14"/>
       <c r="N4" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="B5" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" s="8">
         <f>Budget!H5</f>
-        <v>481250</v>
+        <v>375550</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F5" s="17">
         <f>'BOM&amp;ASP'!F3</f>
@@ -7734,7 +8197,7 @@
         <v>212.47787610619471</v>
       </c>
       <c r="M5" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N5" s="22">
         <f>G22</f>
@@ -7743,14 +8206,14 @@
     </row>
     <row r="6" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="B6" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" s="8">
         <f>Budget!H6</f>
-        <v>159000</v>
+        <v>145000</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F6" s="24">
         <f t="shared" ref="F6:J6" si="1">$C$16+$C$17</f>
@@ -7777,9 +8240,9 @@
         <v>0</v>
       </c>
       <c r="M6" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="N6" s="135">
+        <v>76</v>
+      </c>
+      <c r="N6" s="134">
         <f>(N5-N7)/N5</f>
         <v>0.48695479969176236</v>
       </c>
@@ -7793,15 +8256,15 @@
         <v>150000</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F7" s="24">
         <f>(C3+C4-D3)/C20</f>
-        <v>78.273809523809518</v>
+        <v>76.388888888888886</v>
       </c>
       <c r="G7" s="18">
         <f t="shared" ref="G7:K7" si="3">F7/1.13</f>
-        <v>69.268857985672142</v>
+        <v>67.60078662733531</v>
       </c>
       <c r="H7" s="24">
         <v>0</v>
@@ -7818,7 +8281,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N7" s="28">
         <f>G5</f>
@@ -7827,22 +8290,22 @@
     </row>
     <row r="8" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="B8" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" s="8">
         <f>Budget!H8</f>
-        <v>2032800</v>
+        <v>3003000</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F8" s="24">
         <f>(C9-C3-C4)/C20</f>
-        <v>168.03869047619048</v>
+        <v>255.10763888888889</v>
       </c>
       <c r="G8" s="18">
         <f>F8/1.13</f>
-        <v>148.70680573114203</v>
+        <v>225.75897246804328</v>
       </c>
       <c r="H8" s="24">
         <v>0</v>
@@ -7859,20 +8322,20 @@
         <v>0</v>
       </c>
       <c r="M8" s="27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N8" s="29"/>
     </row>
     <row r="9" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="B9" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" s="31">
         <f>SUM(C3:C8)</f>
-        <v>4138050</v>
+        <v>4773550</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F9" s="32">
         <v>0</v>
@@ -7898,16 +8361,16 @@
         <v>0</v>
       </c>
       <c r="M9" s="27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N9" s="33">
         <f>SUM(C20:C26)</f>
-        <v>50400</v>
+        <v>43200</v>
       </c>
     </row>
     <row r="10" spans="2:26" s="1" customFormat="1" ht="15.6">
       <c r="E10" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F10" s="34">
         <v>0.57999999999999996</v>
@@ -7933,22 +8396,22 @@
         <v>0.53211009174311896</v>
       </c>
       <c r="M10" s="27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N10" s="35">
         <f>G28+I28+K28</f>
-        <v>21215516.1179469</v>
+        <v>18184728.101097342</v>
       </c>
     </row>
     <row r="11" spans="2:26" ht="15.6">
       <c r="B11" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="36">
+        <v>0</v>
+      </c>
+      <c r="E11" s="23" t="s">
         <v>88</v>
-      </c>
-      <c r="C11" s="36">
-        <v>0</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>89</v>
       </c>
       <c r="F11" s="24">
         <f t="shared" ref="F11:K11" si="7">F10+F9</f>
@@ -7975,23 +8438,23 @@
         <v>0.53211009174311896</v>
       </c>
       <c r="M11" s="27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N11" s="35">
         <f>G23*G27+I23*I27+K23*K27</f>
-        <v>10286595.763964599</v>
+        <v>8817082.0833982266</v>
       </c>
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="2:26" ht="15.6">
       <c r="B12" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="40">
+        <v>0</v>
+      </c>
+      <c r="E12" s="16" t="s">
         <v>91</v>
-      </c>
-      <c r="C12" s="40">
-        <v>0</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>92</v>
       </c>
       <c r="F12" s="41">
         <v>0.05</v>
@@ -8015,7 +8478,7 @@
         <v>0.05</v>
       </c>
       <c r="M12" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N12" s="45">
         <f>N11/N10</f>
@@ -8024,13 +8487,13 @@
     </row>
     <row r="13" spans="2:26" s="2" customFormat="1" ht="15.6">
       <c r="B13" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="40">
+        <v>0</v>
+      </c>
+      <c r="E13" s="23" t="s">
         <v>94</v>
-      </c>
-      <c r="C13" s="40">
-        <v>0</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>95</v>
       </c>
       <c r="F13" s="24">
         <f t="shared" ref="F13:J13" si="9">F12*F5</f>
@@ -8057,22 +8520,22 @@
         <v>12.005000000000001</v>
       </c>
       <c r="M13" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N13" s="35">
         <f>G29+I29+K29</f>
-        <v>-1463063.6212096228</v>
+        <v>-2339585.5059167193</v>
       </c>
     </row>
     <row r="14" spans="2:26" s="3" customFormat="1" ht="15.6">
       <c r="B14" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="40">
+        <v>0</v>
+      </c>
+      <c r="E14" s="16" t="s">
         <v>97</v>
-      </c>
-      <c r="C14" s="40">
-        <v>0</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>98</v>
       </c>
       <c r="F14" s="41">
         <v>1.7000000000000001E-2</v>
@@ -8098,22 +8561,22 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="M14" s="26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N14" s="46">
         <f>N13/N10</f>
-        <v>-6.8961962229708351E-2</v>
+        <v>-0.12865661190587388</v>
       </c>
     </row>
     <row r="15" spans="2:26" s="3" customFormat="1" ht="15.6">
       <c r="B15" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="40">
+        <v>0</v>
+      </c>
+      <c r="E15" s="23" t="s">
         <v>100</v>
-      </c>
-      <c r="C15" s="40">
-        <v>0</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>101</v>
       </c>
       <c r="F15" s="24">
         <f>C28*F14</f>
@@ -8140,23 +8603,23 @@
         <v>3.7610619469026552</v>
       </c>
       <c r="M15" s="21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N15" s="47">
         <f>C9</f>
-        <v>4138050</v>
+        <v>4773550</v>
       </c>
     </row>
     <row r="16" spans="2:26" s="3" customFormat="1" ht="15.6">
       <c r="B16" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C16" s="48">
         <f>SUM(C11:C15)</f>
         <v>0</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F16" s="24">
         <f t="shared" ref="F16:K16" si="13">F15</f>
@@ -8183,22 +8646,22 @@
         <v>3.7610619469026552</v>
       </c>
       <c r="M16" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="N16" s="49">
+        <v>104</v>
+      </c>
+      <c r="N16" s="162">
         <f>N13/N15</f>
-        <v>-0.35356354350711633</v>
+        <v>-0.49011438152249781</v>
       </c>
     </row>
     <row r="17" spans="2:14" s="3" customFormat="1" ht="15.6">
       <c r="B17" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="49">
+        <v>0</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>106</v>
-      </c>
-      <c r="C17" s="50">
-        <v>0</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>107</v>
       </c>
       <c r="F17" s="41">
         <v>5.0000000000000001E-3</v>
@@ -8221,7 +8684,7 @@
     </row>
     <row r="18" spans="2:14">
       <c r="E18" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F18" s="24">
         <f t="shared" ref="F18:J18" si="14">F5*F17</f>
@@ -8249,11 +8712,11 @@
       </c>
     </row>
     <row r="19" spans="2:14" ht="15.6">
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>109</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>110</v>
       </c>
       <c r="F19" s="41">
         <v>0.3</v>
@@ -8276,15 +8739,15 @@
     </row>
     <row r="20" spans="2:14">
       <c r="B20" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="52">
+        <v>110</v>
+      </c>
+      <c r="C20" s="51">
         <f>Scenarios!C20</f>
-        <v>16800</v>
+        <v>14400</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F20" s="24">
         <f t="shared" ref="F20:J20" si="16">F19*F22</f>
@@ -8310,29 +8773,29 @@
         <f t="shared" si="17"/>
         <v>139.53262637999995</v>
       </c>
-      <c r="M20" s="156">
+      <c r="M20" s="155">
         <f>F20*C20+H20*C21+J20*C22</f>
-        <v>7192059.9639839977</v>
+        <v>6164622.8262719978</v>
       </c>
     </row>
     <row r="21" spans="2:14" s="3" customFormat="1" ht="15.6">
       <c r="B21" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="52">
+        <f>Scenarios!C21</f>
+        <v>14400</v>
+      </c>
+      <c r="E21" s="53" t="s">
         <v>113</v>
-      </c>
-      <c r="C21" s="53">
-        <f>Scenarios!C21</f>
-        <v>16800</v>
-      </c>
-      <c r="E21" s="54" t="s">
-        <v>114</v>
       </c>
       <c r="F21" s="24">
         <f t="shared" ref="F21:K21" si="18">F5+F6++F7+F8+F11+F13+F16+F18+F20</f>
-        <v>661.07844999999986</v>
+        <v>746.2624777777778</v>
       </c>
       <c r="G21" s="18">
         <f t="shared" si="18"/>
-        <v>603.44372380855725</v>
+        <v>678.82781918712169</v>
       </c>
       <c r="H21" s="37">
         <f t="shared" si="18"/>
@@ -8353,20 +8816,20 @@
     </row>
     <row r="22" spans="2:14" ht="15.6">
       <c r="B22" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22" s="53">
+        <v>114</v>
+      </c>
+      <c r="C22" s="52">
         <f>Scenarios!C22</f>
-        <v>16800</v>
+        <v>14400</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F22" s="17">
         <f>'BOM&amp;ASP'!C10</f>
         <v>487.28649999999993</v>
       </c>
-      <c r="G22" s="55">
+      <c r="G22" s="54">
         <f t="shared" ref="G22:K22" si="19">F22/1.13</f>
         <v>431.22699115044247</v>
       </c>
@@ -8374,7 +8837,7 @@
         <f>(F22-3)*0.98</f>
         <v>474.6007699999999</v>
       </c>
-      <c r="I22" s="56">
+      <c r="I22" s="55">
         <f t="shared" si="19"/>
         <v>420.00068141592914</v>
       </c>
@@ -8382,16 +8845,16 @@
         <f>H22*0.98</f>
         <v>465.10875459999988</v>
       </c>
-      <c r="K22" s="57">
+      <c r="K22" s="56">
         <f t="shared" si="19"/>
         <v>411.60066778761058</v>
       </c>
     </row>
     <row r="23" spans="2:14">
       <c r="B23" s="7"/>
-      <c r="C23" s="58"/>
+      <c r="C23" s="57"/>
       <c r="E23" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F23" s="24">
         <f t="shared" ref="F23:K23" si="20">F22-F5</f>
@@ -8420,15 +8883,15 @@
     </row>
     <row r="24" spans="2:14" ht="15.6">
       <c r="B24" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="58">
+        <v>0</v>
+      </c>
+      <c r="E24" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="C24" s="59">
-        <v>0</v>
-      </c>
-      <c r="E24" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="F24" s="60">
+      <c r="F24" s="59">
         <f t="shared" ref="F24:K24" si="21">F23/F22</f>
         <v>0.48695479969176236</v>
       </c>
@@ -8436,7 +8899,7 @@
         <f t="shared" si="21"/>
         <v>0.48695479969176236</v>
       </c>
-      <c r="H24" s="60">
+      <c r="H24" s="59">
         <f t="shared" si="21"/>
         <v>0.4837766487399503</v>
       </c>
@@ -8444,7 +8907,7 @@
         <f t="shared" si="21"/>
         <v>0.4837766487399503</v>
       </c>
-      <c r="J24" s="60">
+      <c r="J24" s="59">
         <f t="shared" si="21"/>
         <v>0.4837766487399503</v>
       </c>
@@ -8455,21 +8918,21 @@
     </row>
     <row r="25" spans="2:14">
       <c r="B25" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="58">
+        <v>0</v>
+      </c>
+      <c r="E25" s="23" t="s">
         <v>119</v>
-      </c>
-      <c r="C25" s="59">
-        <v>0</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>120</v>
       </c>
       <c r="F25" s="24">
         <f t="shared" ref="F25:K25" si="22">F22-F21</f>
-        <v>-173.79194999999993</v>
+        <v>-258.97597777777787</v>
       </c>
       <c r="G25" s="18">
         <f t="shared" si="22"/>
-        <v>-172.21673265811478</v>
+        <v>-247.60082803667922</v>
       </c>
       <c r="H25" s="24">
         <f t="shared" si="22"/>
@@ -8490,23 +8953,23 @@
     </row>
     <row r="26" spans="2:14" ht="15.6">
       <c r="B26" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="60">
+        <v>0</v>
+      </c>
+      <c r="E26" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="C26" s="61">
-        <v>0</v>
-      </c>
-      <c r="E26" s="54" t="s">
-        <v>122</v>
-      </c>
-      <c r="F26" s="60">
+      <c r="F26" s="59">
         <f t="shared" ref="F26:K26" si="23">F25/F22</f>
-        <v>-0.35665250319883673</v>
+        <v>-0.53146552957608695</v>
       </c>
       <c r="G26" s="42">
         <f t="shared" si="23"/>
-        <v>-0.39936445582561736</v>
-      </c>
-      <c r="H26" s="60">
+        <v>-0.57417748220286735</v>
+      </c>
+      <c r="H26" s="59">
         <f t="shared" si="23"/>
         <v>0.14520738978152073</v>
       </c>
@@ -8514,7 +8977,7 @@
         <f t="shared" si="23"/>
         <v>0.10247154585596281</v>
       </c>
-      <c r="J26" s="60">
+      <c r="J26" s="59">
         <f t="shared" si="23"/>
         <v>0.14499969642153876</v>
       </c>
@@ -8526,115 +8989,115 @@
       <c r="N26" s="3"/>
     </row>
     <row r="27" spans="2:14" ht="15.6">
-      <c r="E27" s="54" t="s">
-        <v>123</v>
-      </c>
-      <c r="F27" s="62">
+      <c r="E27" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" s="61">
         <f>C20+C24</f>
-        <v>16800</v>
-      </c>
-      <c r="G27" s="63">
+        <v>14400</v>
+      </c>
+      <c r="G27" s="62">
         <f t="shared" ref="G27:K27" si="24">F27</f>
-        <v>16800</v>
-      </c>
-      <c r="H27" s="64">
+        <v>14400</v>
+      </c>
+      <c r="H27" s="63">
         <f>C21+C25</f>
-        <v>16800</v>
-      </c>
-      <c r="I27" s="65">
+        <v>14400</v>
+      </c>
+      <c r="I27" s="64">
         <f t="shared" si="24"/>
-        <v>16800</v>
-      </c>
-      <c r="J27" s="64">
+        <v>14400</v>
+      </c>
+      <c r="J27" s="63">
         <f>C22+C26</f>
-        <v>16800</v>
-      </c>
-      <c r="K27" s="66">
+        <v>14400</v>
+      </c>
+      <c r="K27" s="65">
         <f t="shared" si="24"/>
-        <v>16800</v>
-      </c>
-      <c r="M27" s="67"/>
-      <c r="N27" s="67"/>
+        <v>14400</v>
+      </c>
+      <c r="M27" s="66"/>
+      <c r="N27" s="66"/>
     </row>
     <row r="28" spans="2:14" ht="15.6">
       <c r="B28" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C28" s="36">
         <f>F5</f>
         <v>250</v>
       </c>
-      <c r="E28" s="54" t="s">
-        <v>125</v>
-      </c>
-      <c r="F28" s="68">
+      <c r="E28" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" s="67">
         <f t="shared" ref="F28:K28" si="25">F27*F22</f>
-        <v>8186413.1999999993</v>
+        <v>7016925.5999999987</v>
       </c>
       <c r="G28" s="18">
         <f t="shared" si="25"/>
-        <v>7244613.4513274338</v>
-      </c>
-      <c r="H28" s="69">
+        <v>6209668.672566372</v>
+      </c>
+      <c r="H28" s="68">
         <f t="shared" si="25"/>
-        <v>7973292.9359999979</v>
-      </c>
-      <c r="I28" s="70">
+        <v>6834251.0879999986</v>
+      </c>
+      <c r="I28" s="69">
         <f t="shared" si="25"/>
-        <v>7056011.4477876099</v>
-      </c>
-      <c r="J28" s="69">
+        <v>6048009.8123893794</v>
+      </c>
+      <c r="J28" s="68">
         <f t="shared" si="25"/>
-        <v>7813827.077279998</v>
-      </c>
-      <c r="K28" s="71">
+        <v>6697566.0662399987</v>
+      </c>
+      <c r="K28" s="70">
         <f t="shared" si="25"/>
-        <v>6914891.2188318577</v>
+        <v>5927049.6161415922</v>
       </c>
     </row>
     <row r="29" spans="2:14" ht="15.6">
       <c r="B29" s="30"/>
-      <c r="C29" s="50"/>
-      <c r="E29" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="F29" s="72">
+      <c r="C29" s="49"/>
+      <c r="E29" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="F29" s="71">
         <f t="shared" ref="F29:K29" si="26">F27*F25</f>
-        <v>-2919704.7599999988</v>
-      </c>
-      <c r="G29" s="73">
+        <v>-3729254.0800000015</v>
+      </c>
+      <c r="G29" s="72">
         <f t="shared" si="26"/>
-        <v>-2893241.1086563282</v>
-      </c>
-      <c r="H29" s="74">
+        <v>-3565451.9237281806</v>
+      </c>
+      <c r="H29" s="73">
         <f t="shared" si="26"/>
-        <v>1157781.0551999975</v>
-      </c>
-      <c r="I29" s="75">
+        <v>992383.76159999787</v>
+      </c>
+      <c r="I29" s="74">
         <f t="shared" si="26"/>
-        <v>723040.40063216665</v>
-      </c>
-      <c r="J29" s="74">
+        <v>619748.91482757137</v>
+      </c>
+      <c r="J29" s="73">
         <f t="shared" si="26"/>
-        <v>1133002.5540959991</v>
-      </c>
-      <c r="K29" s="76">
+        <v>971145.04636799928</v>
+      </c>
+      <c r="K29" s="75">
         <f t="shared" si="26"/>
-        <v>707137.08681453846</v>
+        <v>606117.50298389001</v>
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="77"/>
-      <c r="D39" s="78"/>
+      <c r="A39" s="76"/>
+      <c r="D39" s="77"/>
     </row>
     <row r="40" spans="1:10">
       <c r="D40" s="1"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="D43" s="79"/>
+      <c r="D43" s="78"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="J46" s="51"/>
+      <c r="J46" s="50"/>
     </row>
     <row r="50" spans="8:11">
       <c r="J50" s="1"/>
@@ -8654,7 +9117,7 @@
     </row>
     <row r="54" spans="8:11">
       <c r="J54" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K54" s="1"/>
     </row>
